--- a/output/final_questions.xlsx
+++ b/output/final_questions.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4">
@@ -467,17 +467,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>오류 수정</t>
+          <t>중복 통합(비활성화)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>중복 통합(비활성화)</t>
+          <t>오류 수정</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -712,7 +712,7 @@
         <v>45</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4547422795802848</v>
+        <v>0.4547422827072897</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
@@ -840,7 +840,7 @@
         <v>98</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2458441829848769</v>
+        <v>0.2458441855728337</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
@@ -968,7 +968,7 @@
         <v>46</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4502808655649432</v>
+        <v>0.4502808655268764</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
         <v>78</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2952355501391798</v>
+        <v>0.2952355448848513</v>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1694,7 +1694,7 @@
         <v>100</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2378700107126246</v>
+        <v>0.2378700102547778</v>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -1968,7 +1968,7 @@
         <v>146</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1500068943811977</v>
+        <v>0.1500068961205726</v>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
         <v>39</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.4842197466555238</v>
+        <v>0.4842197424207495</v>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
@@ -2576,7 +2576,7 @@
         <v>57</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.377145420176954</v>
+        <v>0.3771454261577982</v>
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -2647,7 +2647,7 @@
         <v>106</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2241666282526584</v>
+        <v>0.2241666297228008</v>
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -3031,7 +3031,7 @@
         <v>175</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.1139434377582921</v>
+        <v>0.1139434375512308</v>
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -3775,7 +3775,7 @@
         <v>54</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.3834105333822548</v>
+        <v>0.3834105314086291</v>
       </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3913,7 +3913,7 @@
         <v>53</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.3835448518039157</v>
+        <v>0.3835448489416398</v>
       </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
@@ -3984,7 +3984,7 @@
         <v>61</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.3505904872967197</v>
+        <v>0.3505904854216243</v>
       </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
         <v>80</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.2933997665717098</v>
+        <v>0.293399766322991</v>
       </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -4197,7 +4197,7 @@
         <v>17</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.890957956571074</v>
+        <v>0.8909579539612801</v>
       </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
@@ -4268,7 +4268,7 @@
         <v>25</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.6148815606279704</v>
+        <v>0.6148815609814982</v>
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -4339,7 +4339,7 @@
         <v>177</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.1072784959373221</v>
+        <v>0.1072784961265131</v>
       </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
@@ -4410,7 +4410,7 @@
         <v>107</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.2238903561463012</v>
+        <v>0.223890354536146</v>
       </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -4481,7 +4481,7 @@
         <v>22</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.7197976797460508</v>
+        <v>0.7197976763994859</v>
       </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
@@ -4552,7 +4552,7 @@
         <v>60</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.3524293163366528</v>
+        <v>0.3524293192803396</v>
       </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
@@ -4623,7 +4623,7 @@
         <v>150</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.1447818810279481</v>
+        <v>0.1447818809615887</v>
       </c>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
         <v>21</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.792561416095188</v>
+        <v>0.7925614174428081</v>
       </c>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
@@ -4879,7 +4879,7 @@
         <v>34</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.538021365436351</v>
+        <v>0.5380213657727635</v>
       </c>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
@@ -4950,7 +4950,7 @@
         <v>14</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.9619489795446871</v>
+        <v>0.9619489740657668</v>
       </c>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
         <v>48</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.4256712508539423</v>
+        <v>0.4256712509831923</v>
       </c>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
@@ -5391,7 +5391,7 @@
         <v>220</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.07383368994968489</v>
+        <v>0.07383368915694639</v>
       </c>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
@@ -5633,7 +5633,7 @@
         <v>55</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.3796124968690004</v>
+        <v>0.3796124956301423</v>
       </c>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
@@ -5704,7 +5704,7 @@
         <v>50</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.4237762756483722</v>
+        <v>0.4237762754376256</v>
       </c>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
@@ -5775,7 +5775,7 @@
         <v>13</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9990980208916074</v>
+        <v>0.9990980198416328</v>
       </c>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
         <v>27</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.6038899530473893</v>
+        <v>0.6038899553065709</v>
       </c>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
@@ -5917,7 +5917,7 @@
         <v>174</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.1141709208919321</v>
+        <v>0.114170921614333</v>
       </c>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
@@ -5988,7 +5988,7 @@
         <v>154</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.1403365387018615</v>
+        <v>0.1403365386805624</v>
       </c>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
@@ -6059,7 +6059,7 @@
         <v>90</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.2658867873580479</v>
+        <v>0.2658867831585775</v>
       </c>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr"/>
@@ -6130,7 +6130,7 @@
         <v>287</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.0017276241512694</v>
+        <v>0.0017276241473718</v>
       </c>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr"/>
@@ -6201,7 +6201,7 @@
         <v>267</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.0193445398173798</v>
+        <v>0.0193445397733174</v>
       </c>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr"/>
@@ -6329,7 +6329,7 @@
         <v>30</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.5723008783133967</v>
+        <v>0.5723008773777398</v>
       </c>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr"/>
@@ -6467,7 +6467,7 @@
         <v>243</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.050173175463388</v>
+        <v>0.0501731751374618</v>
       </c>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr"/>
@@ -6666,7 +6666,7 @@
         <v>49</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.4241336509710668</v>
+        <v>0.4241336473150646</v>
       </c>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr"/>
@@ -6737,7 +6737,7 @@
         <v>69</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.3189343991839057</v>
+        <v>0.3189343995726886</v>
       </c>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr"/>
@@ -6808,7 +6808,7 @@
         <v>244</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.0481432549890464</v>
+        <v>0.0481432550528766</v>
       </c>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr"/>
@@ -7092,7 +7092,7 @@
         <v>203</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.0825546771768009</v>
+        <v>0.0825546766316614</v>
       </c>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr"/>
@@ -7291,7 +7291,7 @@
         <v>156</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.1392376426816677</v>
+        <v>0.1392376422468438</v>
       </c>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
@@ -7543,7 +7543,7 @@
         <v>208</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.0801809548459565</v>
+        <v>0.08018095465931969</v>
       </c>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr"/>
@@ -7781,7 +7781,7 @@
         <v>26</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.6119960197306289</v>
+        <v>0.6119960167838771</v>
       </c>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr"/>
@@ -7966,7 +7966,7 @@
         <v>224</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.06930730229210121</v>
+        <v>0.0693073021656844</v>
       </c>
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr"/>
@@ -8094,7 +8094,7 @@
         <v>33</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.5571099705686849</v>
+        <v>0.5571099671060507</v>
       </c>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr"/>
@@ -8279,7 +8279,7 @@
         <v>127</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.179708830224044</v>
+        <v>0.1797088297467197</v>
       </c>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
         <v>95</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.2479276168587277</v>
+        <v>0.2479276167380216</v>
       </c>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr"/>
@@ -8592,7 +8592,7 @@
         <v>119</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.1906176010839483</v>
+        <v>0.190617602778101</v>
       </c>
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr"/>
@@ -8663,7 +8663,7 @@
         <v>68</v>
       </c>
       <c r="Q125" t="n">
-        <v>0.3215107754217839</v>
+        <v>0.3215107748327863</v>
       </c>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr"/>
@@ -8734,7 +8734,7 @@
         <v>113</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.2036146719632358</v>
+        <v>0.2036146721281323</v>
       </c>
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr"/>
@@ -8805,7 +8805,7 @@
         <v>164</v>
       </c>
       <c r="Q127" t="n">
-        <v>0.1301966711031801</v>
+        <v>0.1301966712260819</v>
       </c>
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr"/>
@@ -8876,7 +8876,7 @@
         <v>66</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.3275821210119635</v>
+        <v>0.3275821219554654</v>
       </c>
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr"/>
@@ -8947,7 +8947,7 @@
         <v>79</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.2942367290838963</v>
+        <v>0.2942367286049314</v>
       </c>
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr"/>
@@ -9018,7 +9018,7 @@
         <v>59</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.363198427573286</v>
+        <v>0.3631984251391726</v>
       </c>
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr"/>
@@ -9203,7 +9203,7 @@
         <v>179</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.1071315123390006</v>
+        <v>0.1071315122600101</v>
       </c>
       <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr"/>
@@ -9274,7 +9274,7 @@
         <v>234</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.0635033219480422</v>
+        <v>0.0635033217975645</v>
       </c>
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr"/>
@@ -9473,7 +9473,7 @@
         <v>109</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.2190980108249647</v>
+        <v>0.2190980103425579</v>
       </c>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr"/>
@@ -9601,7 +9601,7 @@
         <v>103</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.2285397966876771</v>
+        <v>0.2285397961866024</v>
       </c>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr"/>
@@ -9729,7 +9729,7 @@
         <v>228</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.0673547693325488</v>
+        <v>0.06735476911548249</v>
       </c>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr"/>
@@ -10213,7 +10213,7 @@
         <v>88</v>
       </c>
       <c r="Q149" t="n">
-        <v>0.2696155517040787</v>
+        <v>0.2696155518392379</v>
       </c>
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr"/>
@@ -10355,7 +10355,7 @@
         <v>141</v>
       </c>
       <c r="Q151" t="n">
-        <v>0.158086383108305</v>
+        <v>0.158086382300763</v>
       </c>
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr"/>
@@ -10426,7 +10426,7 @@
         <v>230</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.06612873571937621</v>
+        <v>0.06612873594133151</v>
       </c>
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr"/>
@@ -10568,7 +10568,7 @@
         <v>189</v>
       </c>
       <c r="Q154" t="n">
-        <v>0.09719655074945049</v>
+        <v>0.09719655157010031</v>
       </c>
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
         <v>152</v>
       </c>
       <c r="Q156" t="n">
-        <v>0.1409626221306283</v>
+        <v>0.1409626206519375</v>
       </c>
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr"/>
@@ -10923,7 +10923,7 @@
         <v>202</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.0827757435141263</v>
+        <v>0.08277574395294821</v>
       </c>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr"/>
@@ -10994,7 +10994,7 @@
         <v>160</v>
       </c>
       <c r="Q160" t="n">
-        <v>0.1375912581031854</v>
+        <v>0.1375912580325612</v>
       </c>
       <c r="R160" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>169</v>
       </c>
       <c r="Q166" t="n">
-        <v>0.1249721423949838</v>
+        <v>0.1249721423551462</v>
       </c>
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
         <v>256</v>
       </c>
       <c r="Q176" t="n">
-        <v>0.0326479158368244</v>
+        <v>0.032647915462264</v>
       </c>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr"/>
@@ -12175,7 +12175,7 @@
         <v>211</v>
       </c>
       <c r="Q179" t="n">
-        <v>0.0767586737396341</v>
+        <v>0.0767586738019542</v>
       </c>
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr"/>
@@ -12488,7 +12488,7 @@
         <v>104</v>
       </c>
       <c r="Q184" t="n">
-        <v>0.227248354773365</v>
+        <v>0.2272483545663617</v>
       </c>
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr"/>
@@ -12616,7 +12616,7 @@
         <v>222</v>
       </c>
       <c r="Q186" t="n">
-        <v>0.0724339413999564</v>
+        <v>0.0724339414044214</v>
       </c>
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr"/>
@@ -12801,7 +12801,7 @@
         <v>252</v>
       </c>
       <c r="Q189" t="n">
-        <v>0.0375527686976297</v>
+        <v>0.0375527691823863</v>
       </c>
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr"/>
@@ -12929,7 +12929,7 @@
         <v>125</v>
       </c>
       <c r="Q191" t="n">
-        <v>0.1832889705191899</v>
+        <v>0.1832889687857333</v>
       </c>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
         <v>199</v>
       </c>
       <c r="Q194" t="n">
-        <v>0.0852199679854896</v>
+        <v>0.08521996719658539</v>
       </c>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
@@ -13284,7 +13284,7 @@
         <v>283</v>
       </c>
       <c r="Q196" t="n">
-        <v>0.0053799651642695</v>
+        <v>0.0053799652033142</v>
       </c>
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr"/>
@@ -13469,7 +13469,7 @@
         <v>286</v>
       </c>
       <c r="Q199" t="n">
-        <v>0.0018666987473211</v>
+        <v>0.0018666987493512</v>
       </c>
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
         <v>274</v>
       </c>
       <c r="Q206" t="n">
-        <v>0.0122052657109853</v>
+        <v>0.0122052657630616</v>
       </c>
       <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr"/>
@@ -14290,7 +14290,7 @@
         <v>166</v>
       </c>
       <c r="Q212" t="n">
-        <v>0.1271754709459482</v>
+        <v>0.127175471632148</v>
       </c>
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr"/>
@@ -14414,7 +14414,7 @@
         <v>120</v>
       </c>
       <c r="Q214" t="n">
-        <v>0.1891131987801722</v>
+        <v>0.1891131987750259</v>
       </c>
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr"/>
@@ -14485,7 +14485,7 @@
         <v>117</v>
       </c>
       <c r="Q215" t="n">
-        <v>0.1918969139526298</v>
+        <v>0.1918969138800904</v>
       </c>
       <c r="R215" t="inlineStr"/>
       <c r="S215" t="inlineStr"/>
@@ -14784,7 +14784,7 @@
         <v>82</v>
       </c>
       <c r="Q220" t="n">
-        <v>0.2857281937139234</v>
+        <v>0.2857281935592242</v>
       </c>
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr"/>
@@ -14855,7 +14855,7 @@
         <v>277</v>
       </c>
       <c r="Q221" t="n">
-        <v>0.010312248775314</v>
+        <v>0.0103122488576046</v>
       </c>
       <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr"/>
@@ -15339,7 +15339,7 @@
         <v>162</v>
       </c>
       <c r="Q229" t="n">
-        <v>0.1370474516710556</v>
+        <v>0.1370474516405825</v>
       </c>
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr"/>
@@ -15406,7 +15406,7 @@
         <v>138</v>
       </c>
       <c r="Q230" t="n">
-        <v>0.1618642019419722</v>
+        <v>0.1618642026020011</v>
       </c>
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr"/>
@@ -15534,7 +15534,7 @@
         <v>183</v>
       </c>
       <c r="Q232" t="n">
-        <v>0.1025553819711048</v>
+        <v>0.1025553820530929</v>
       </c>
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr"/>
@@ -15776,7 +15776,7 @@
         <v>285</v>
       </c>
       <c r="Q236" t="n">
-        <v>0.0034161649124316</v>
+        <v>0.0034161649279003</v>
       </c>
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr"/>
@@ -15904,7 +15904,7 @@
         <v>276</v>
       </c>
       <c r="Q238" t="n">
-        <v>0.0117431250808903</v>
+        <v>0.0117431250742536</v>
       </c>
       <c r="R238" t="inlineStr"/>
       <c r="S238" t="inlineStr"/>
@@ -16384,7 +16384,7 @@
         <v>147</v>
       </c>
       <c r="Q246" t="n">
-        <v>0.1482861990191183</v>
+        <v>0.148286199366885</v>
       </c>
       <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr"/>
@@ -16512,7 +16512,7 @@
         <v>233</v>
       </c>
       <c r="Q248" t="n">
-        <v>0.0639326509939145</v>
+        <v>0.0639326509274414</v>
       </c>
       <c r="R248" t="inlineStr"/>
       <c r="S248" t="inlineStr"/>
@@ -17476,7 +17476,7 @@
         <v>221</v>
       </c>
       <c r="Q264" t="n">
-        <v>0.0731246733588764</v>
+        <v>0.0731246732899037</v>
       </c>
       <c r="R264" t="inlineStr"/>
       <c r="S264" t="inlineStr"/>
@@ -17789,7 +17789,7 @@
         <v>263</v>
       </c>
       <c r="Q269" t="n">
-        <v>0.023549418090304</v>
+        <v>0.0235494180638203</v>
       </c>
       <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr"/>
@@ -17927,7 +17927,7 @@
         <v>186</v>
       </c>
       <c r="Q271" t="n">
-        <v>0.1004758865645845</v>
+        <v>0.1004758864729852</v>
       </c>
       <c r="R271" t="inlineStr"/>
       <c r="S271" t="inlineStr"/>
@@ -17998,7 +17998,7 @@
         <v>180</v>
       </c>
       <c r="Q272" t="n">
-        <v>0.1057158327925083</v>
+        <v>0.1057158324343914</v>
       </c>
       <c r="R272" t="inlineStr"/>
       <c r="S272" t="inlineStr"/>
@@ -19173,7 +19173,7 @@
         <v>209</v>
       </c>
       <c r="Q291" t="n">
-        <v>0.0780979712771229</v>
+        <v>0.0780979713100205</v>
       </c>
       <c r="R291" t="inlineStr"/>
       <c r="S291" t="inlineStr"/>
@@ -19244,7 +19244,7 @@
         <v>130</v>
       </c>
       <c r="Q292" t="n">
-        <v>0.1749532200661109</v>
+        <v>0.1749532196644946</v>
       </c>
       <c r="R292" t="inlineStr"/>
       <c r="S292" t="inlineStr"/>
@@ -19311,7 +19311,7 @@
         <v>161</v>
       </c>
       <c r="Q293" t="n">
-        <v>0.1375844245017798</v>
+        <v>0.1375844243827706</v>
       </c>
       <c r="R293" t="inlineStr"/>
       <c r="S293" t="inlineStr"/>
@@ -19795,7 +19795,7 @@
         <v>226</v>
       </c>
       <c r="Q301" t="n">
-        <v>0.06790158709530091</v>
+        <v>0.0679015868006366</v>
       </c>
       <c r="R301" t="inlineStr"/>
       <c r="S301" t="inlineStr"/>
@@ -19866,7 +19866,7 @@
         <v>32</v>
       </c>
       <c r="Q302" t="n">
-        <v>0.5627712299973278</v>
+        <v>0.5627712315558411</v>
       </c>
       <c r="R302" t="inlineStr"/>
       <c r="S302" t="inlineStr"/>
@@ -20179,7 +20179,7 @@
         <v>44</v>
       </c>
       <c r="Q307" t="n">
-        <v>0.4592891442365296</v>
+        <v>0.4592891445559759</v>
       </c>
       <c r="R307" t="inlineStr"/>
       <c r="S307" t="inlineStr"/>
@@ -20734,7 +20734,7 @@
         <v>19</v>
       </c>
       <c r="Q316" t="n">
-        <v>0.8210638736723673</v>
+        <v>0.8210638608013721</v>
       </c>
       <c r="R316" t="inlineStr"/>
       <c r="S316" t="inlineStr"/>
@@ -21047,7 +21047,7 @@
         <v>65</v>
       </c>
       <c r="Q321" t="n">
-        <v>0.3330792580261453</v>
+        <v>0.3330792601913626</v>
       </c>
       <c r="R321" t="inlineStr"/>
       <c r="S321" t="inlineStr"/>
@@ -21374,7 +21374,7 @@
         <v>37</v>
       </c>
       <c r="Q326" t="n">
-        <v>0.4975762147374358</v>
+        <v>0.4975762132884682</v>
       </c>
       <c r="R326" t="inlineStr"/>
       <c r="S326" t="inlineStr"/>
@@ -21772,7 +21772,7 @@
         <v>84</v>
       </c>
       <c r="Q332" t="n">
-        <v>0.2815577213305332</v>
+        <v>0.2815577188726843</v>
       </c>
       <c r="R332" t="inlineStr"/>
       <c r="S332" t="inlineStr"/>
@@ -21843,7 +21843,7 @@
         <v>2</v>
       </c>
       <c r="Q333" t="n">
-        <v>1.919242557603348</v>
+        <v>1.919242556165218</v>
       </c>
       <c r="R333" t="inlineStr"/>
       <c r="S333" t="inlineStr"/>
@@ -21914,7 +21914,7 @@
         <v>1</v>
       </c>
       <c r="Q334" t="n">
-        <v>2.556123444338013</v>
+        <v>2.556123390077762</v>
       </c>
       <c r="R334" t="inlineStr"/>
       <c r="S334" t="inlineStr"/>
@@ -21981,7 +21981,7 @@
         <v>284</v>
       </c>
       <c r="Q335" t="n">
-        <v>0.0044335539387392</v>
+        <v>0.0044335539091265</v>
       </c>
       <c r="R335" t="inlineStr"/>
       <c r="S335" t="inlineStr"/>
@@ -22052,7 +22052,7 @@
         <v>10</v>
       </c>
       <c r="Q336" t="n">
-        <v>1.140998066750707</v>
+        <v>1.140998074803683</v>
       </c>
       <c r="R336" t="inlineStr"/>
       <c r="S336" t="inlineStr"/>
@@ -22123,7 +22123,7 @@
         <v>140</v>
       </c>
       <c r="Q337" t="n">
-        <v>0.1582518596799811</v>
+        <v>0.1582518595607535</v>
       </c>
       <c r="R337" t="inlineStr"/>
       <c r="S337" t="inlineStr"/>
@@ -22194,7 +22194,7 @@
         <v>3</v>
       </c>
       <c r="Q338" t="n">
-        <v>1.880651429423544</v>
+        <v>1.880651420627575</v>
       </c>
       <c r="R338" t="inlineStr"/>
       <c r="S338" t="inlineStr"/>
@@ -22265,7 +22265,7 @@
         <v>7</v>
       </c>
       <c r="Q339" t="n">
-        <v>1.469741870674143</v>
+        <v>1.469741850150696</v>
       </c>
       <c r="R339" t="inlineStr"/>
       <c r="S339" t="inlineStr"/>
@@ -22621,7 +22621,7 @@
         <v>8</v>
       </c>
       <c r="Q345" t="n">
-        <v>1.377636632610227</v>
+        <v>1.377636642232281</v>
       </c>
       <c r="R345" t="inlineStr"/>
       <c r="S345" t="inlineStr"/>
@@ -22692,7 +22692,7 @@
         <v>43</v>
       </c>
       <c r="Q346" t="n">
-        <v>0.4599585349714158</v>
+        <v>0.4599585288063763</v>
       </c>
       <c r="R346" t="inlineStr"/>
       <c r="S346" t="inlineStr"/>
@@ -22830,7 +22830,7 @@
         <v>9</v>
       </c>
       <c r="Q348" t="n">
-        <v>1.282669810425036</v>
+        <v>1.282669819237425</v>
       </c>
       <c r="R348" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>31</v>
       </c>
       <c r="Q349" t="n">
-        <v>0.5710199182198941</v>
+        <v>0.5710199165154209</v>
       </c>
       <c r="R349" t="inlineStr"/>
       <c r="S349" t="inlineStr"/>
@@ -23047,7 +23047,7 @@
         <v>28</v>
       </c>
       <c r="Q351" t="n">
-        <v>0.5921875177350278</v>
+        <v>0.5921875166908641</v>
       </c>
       <c r="R351" t="inlineStr"/>
       <c r="S351" t="inlineStr"/>
@@ -23118,7 +23118,7 @@
         <v>85</v>
       </c>
       <c r="Q352" t="n">
-        <v>0.2792724224492394</v>
+        <v>0.2792724228798964</v>
       </c>
       <c r="R352" t="inlineStr"/>
       <c r="S352" t="inlineStr"/>
@@ -23189,7 +23189,7 @@
         <v>217</v>
       </c>
       <c r="Q353" t="n">
-        <v>0.0749492543789326</v>
+        <v>0.07494925401815331</v>
       </c>
       <c r="R353" t="inlineStr"/>
       <c r="S353" t="inlineStr"/>
@@ -23260,7 +23260,7 @@
         <v>12</v>
       </c>
       <c r="Q354" t="n">
-        <v>1.037891299550928</v>
+        <v>1.037891307294819</v>
       </c>
       <c r="R354" t="inlineStr"/>
       <c r="S354" t="inlineStr"/>
@@ -23331,7 +23331,7 @@
         <v>105</v>
       </c>
       <c r="Q355" t="n">
-        <v>0.2242611004723249</v>
+        <v>0.2242611020736249</v>
       </c>
       <c r="R355" t="inlineStr"/>
       <c r="S355" t="inlineStr"/>
@@ -23402,7 +23402,7 @@
         <v>20</v>
       </c>
       <c r="Q356" t="n">
-        <v>0.8126522627706078</v>
+        <v>0.8126522636883518</v>
       </c>
       <c r="R356" t="inlineStr"/>
       <c r="S356" t="inlineStr"/>
@@ -23473,7 +23473,7 @@
         <v>5</v>
       </c>
       <c r="Q357" t="n">
-        <v>1.524198154939078</v>
+        <v>1.524198158396275</v>
       </c>
       <c r="R357" t="inlineStr"/>
       <c r="S357" t="inlineStr"/>
@@ -23544,7 +23544,7 @@
         <v>47</v>
       </c>
       <c r="Q358" t="n">
-        <v>0.4273225220088224</v>
+        <v>0.4273225139056333</v>
       </c>
       <c r="R358" t="inlineStr"/>
       <c r="S358" t="inlineStr"/>
@@ -23615,7 +23615,7 @@
         <v>18</v>
       </c>
       <c r="Q359" t="n">
-        <v>0.8812499624319454</v>
+        <v>0.8812499668146205</v>
       </c>
       <c r="R359" t="inlineStr"/>
       <c r="S359" t="inlineStr"/>
@@ -23686,7 +23686,7 @@
         <v>101</v>
       </c>
       <c r="Q360" t="n">
-        <v>0.2374324536469604</v>
+        <v>0.237432454230313</v>
       </c>
       <c r="R360" t="inlineStr"/>
       <c r="S360" t="inlineStr"/>
@@ -23757,7 +23757,7 @@
         <v>29</v>
       </c>
       <c r="Q361" t="n">
-        <v>0.5898551505653457</v>
+        <v>0.5898551502158805</v>
       </c>
       <c r="R361" t="inlineStr"/>
       <c r="S361" t="inlineStr"/>
@@ -23828,7 +23828,7 @@
         <v>23</v>
       </c>
       <c r="Q362" t="n">
-        <v>0.6292713720177435</v>
+        <v>0.6292713719927117</v>
       </c>
       <c r="R362" t="inlineStr"/>
       <c r="S362" t="inlineStr"/>
@@ -23899,7 +23899,7 @@
         <v>16</v>
       </c>
       <c r="Q363" t="n">
-        <v>0.8998323860578156</v>
+        <v>0.8998323900340969</v>
       </c>
       <c r="R363" t="inlineStr"/>
       <c r="S363" t="inlineStr"/>
@@ -23970,7 +23970,7 @@
         <v>270</v>
       </c>
       <c r="Q364" t="n">
-        <v>0.0181465185156274</v>
+        <v>0.0181465184721985</v>
       </c>
       <c r="R364" t="inlineStr"/>
       <c r="S364" t="inlineStr"/>
@@ -24041,7 +24041,7 @@
         <v>58</v>
       </c>
       <c r="Q365" t="n">
-        <v>0.3640186819625223</v>
+        <v>0.3640186838368973</v>
       </c>
       <c r="R365" t="inlineStr"/>
       <c r="S365" t="inlineStr"/>
@@ -24112,7 +24112,7 @@
         <v>4</v>
       </c>
       <c r="Q366" t="n">
-        <v>1.777152360622422</v>
+        <v>1.777152407205172</v>
       </c>
       <c r="R366" t="inlineStr"/>
       <c r="S366" t="inlineStr"/>
@@ -24240,7 +24240,7 @@
         <v>196</v>
       </c>
       <c r="Q368" t="n">
-        <v>0.08693091625279541</v>
+        <v>0.0869309193810036</v>
       </c>
       <c r="R368" t="inlineStr"/>
       <c r="S368" t="inlineStr"/>
@@ -24307,7 +24307,7 @@
         <v>237</v>
       </c>
       <c r="Q369" t="n">
-        <v>0.0587628451378995</v>
+        <v>0.0587628452777346</v>
       </c>
       <c r="R369" t="inlineStr"/>
       <c r="S369" t="inlineStr"/>
@@ -24378,7 +24378,7 @@
         <v>6</v>
       </c>
       <c r="Q370" t="n">
-        <v>1.501786877571854</v>
+        <v>1.501786849408398</v>
       </c>
       <c r="R370" t="inlineStr"/>
       <c r="S370" t="inlineStr"/>
@@ -24449,7 +24449,7 @@
         <v>52</v>
       </c>
       <c r="Q371" t="n">
-        <v>0.3962956317693583</v>
+        <v>0.3962956299745762</v>
       </c>
       <c r="R371" t="inlineStr"/>
       <c r="S371" t="inlineStr"/>
@@ -24654,7 +24654,7 @@
         <v>36</v>
       </c>
       <c r="Q374" t="n">
-        <v>0.5076178727371301</v>
+        <v>0.5076178725980323</v>
       </c>
       <c r="R374" t="inlineStr"/>
       <c r="S374" t="inlineStr"/>
@@ -24725,7 +24725,7 @@
         <v>15</v>
       </c>
       <c r="Q375" t="n">
-        <v>0.9400679736331172</v>
+        <v>0.9400679612213904</v>
       </c>
       <c r="R375" t="inlineStr"/>
       <c r="S375" t="inlineStr"/>
@@ -24863,7 +24863,7 @@
         <v>92</v>
       </c>
       <c r="Q377" t="n">
-        <v>0.2534444326551532</v>
+        <v>0.2534444336344664</v>
       </c>
       <c r="R377" t="inlineStr"/>
       <c r="S377" t="inlineStr"/>
@@ -24934,7 +24934,7 @@
         <v>42</v>
       </c>
       <c r="Q378" t="n">
-        <v>0.4743037729558964</v>
+        <v>0.4743037741500181</v>
       </c>
       <c r="R378" t="inlineStr"/>
       <c r="S378" t="inlineStr"/>
@@ -25324,7 +25324,7 @@
         <v>170</v>
       </c>
       <c r="Q384" t="n">
-        <v>0.1236486645090851</v>
+        <v>0.1236486643123691</v>
       </c>
       <c r="R384" t="inlineStr"/>
       <c r="S384" t="inlineStr"/>
@@ -25395,7 +25395,7 @@
         <v>122</v>
       </c>
       <c r="Q385" t="n">
-        <v>0.1866076008168487</v>
+        <v>0.1866076006743147</v>
       </c>
       <c r="R385" t="inlineStr"/>
       <c r="S385" t="inlineStr"/>
@@ -25537,7 +25537,7 @@
         <v>35</v>
       </c>
       <c r="Q387" t="n">
-        <v>0.5095875103746218</v>
+        <v>0.5095875148260584</v>
       </c>
       <c r="R387" t="inlineStr"/>
       <c r="S387" t="inlineStr"/>
@@ -26145,7 +26145,7 @@
         <v>38</v>
       </c>
       <c r="Q397" t="n">
-        <v>0.497183176708147</v>
+        <v>0.4971831752197933</v>
       </c>
       <c r="R397" t="inlineStr"/>
       <c r="S397" t="inlineStr"/>
@@ -26330,7 +26330,7 @@
         <v>262</v>
       </c>
       <c r="Q400" t="n">
-        <v>0.023949491158786</v>
+        <v>0.0239494911621264</v>
       </c>
       <c r="R400" t="inlineStr"/>
       <c r="S400" t="inlineStr"/>
@@ -26458,7 +26458,7 @@
         <v>24</v>
       </c>
       <c r="Q402" t="n">
-        <v>0.6202993920433461</v>
+        <v>0.6202993909659184</v>
       </c>
       <c r="R402" t="inlineStr"/>
       <c r="S402" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
         <v>205</v>
       </c>
       <c r="Q404" t="n">
-        <v>0.0818326987394478</v>
+        <v>0.0818326989764467</v>
       </c>
       <c r="R404" t="inlineStr"/>
       <c r="S404" t="inlineStr"/>
@@ -26724,7 +26724,7 @@
         <v>201</v>
       </c>
       <c r="Q406" t="n">
-        <v>0.0831454502779352</v>
+        <v>0.08314545096709861</v>
       </c>
       <c r="R406" t="inlineStr"/>
       <c r="S406" t="inlineStr"/>
@@ -27456,7 +27456,7 @@
         <v>40</v>
       </c>
       <c r="Q418" t="n">
-        <v>0.4839315754905064</v>
+        <v>0.4839315726841934</v>
       </c>
       <c r="R418" t="inlineStr"/>
       <c r="S418" t="inlineStr"/>
@@ -27584,7 +27584,7 @@
         <v>75</v>
       </c>
       <c r="Q420" t="n">
-        <v>0.2968206886197658</v>
+        <v>0.2968206885285421</v>
       </c>
       <c r="R420" t="inlineStr"/>
       <c r="S420" t="inlineStr"/>
@@ -27826,7 +27826,7 @@
         <v>77</v>
       </c>
       <c r="Q424" t="n">
-        <v>0.2958408817856502</v>
+        <v>0.2958408821914132</v>
       </c>
       <c r="R424" t="inlineStr"/>
       <c r="S424" t="inlineStr"/>
@@ -27954,7 +27954,7 @@
         <v>124</v>
       </c>
       <c r="Q426" t="n">
-        <v>0.1835649749010547</v>
+        <v>0.1835649748183185</v>
       </c>
       <c r="R426" t="inlineStr"/>
       <c r="S426" t="inlineStr"/>
@@ -28025,7 +28025,7 @@
         <v>188</v>
       </c>
       <c r="Q427" t="n">
-        <v>0.0977574325045181</v>
+        <v>0.097757432583382</v>
       </c>
       <c r="R427" t="inlineStr"/>
       <c r="S427" t="inlineStr"/>
@@ -28096,7 +28096,7 @@
         <v>72</v>
       </c>
       <c r="Q428" t="n">
-        <v>0.3017849286286974</v>
+        <v>0.3017849286565414</v>
       </c>
       <c r="R428" t="inlineStr"/>
       <c r="S428" t="inlineStr"/>
@@ -28167,7 +28167,7 @@
         <v>250</v>
       </c>
       <c r="Q429" t="n">
-        <v>0.0386996163281201</v>
+        <v>0.0386996169052657</v>
       </c>
       <c r="R429" t="inlineStr"/>
       <c r="S429" t="inlineStr"/>
@@ -28238,7 +28238,7 @@
         <v>280</v>
       </c>
       <c r="Q430" t="n">
-        <v>0.007856258761746599</v>
+        <v>0.0078562587612958</v>
       </c>
       <c r="R430" t="inlineStr"/>
       <c r="S430" t="inlineStr"/>
@@ -28309,7 +28309,7 @@
         <v>148</v>
       </c>
       <c r="Q431" t="n">
-        <v>0.1472292646650196</v>
+        <v>0.1472292669602828</v>
       </c>
       <c r="R431" t="inlineStr"/>
       <c r="S431" t="inlineStr"/>
@@ -28380,7 +28380,7 @@
         <v>126</v>
       </c>
       <c r="Q432" t="n">
-        <v>0.1831328395882209</v>
+        <v>0.1831328398845251</v>
       </c>
       <c r="R432" t="inlineStr"/>
       <c r="S432" t="inlineStr"/>
@@ -28451,7 +28451,7 @@
         <v>56</v>
       </c>
       <c r="Q433" t="n">
-        <v>0.3776954780160078</v>
+        <v>0.3776954779694583</v>
       </c>
       <c r="R433" t="inlineStr"/>
       <c r="S433" t="inlineStr"/>
@@ -28522,7 +28522,7 @@
         <v>142</v>
       </c>
       <c r="Q434" t="n">
-        <v>0.1570022741214908</v>
+        <v>0.1570022767967323</v>
       </c>
       <c r="R434" t="inlineStr"/>
       <c r="S434" t="inlineStr"/>
@@ -28664,7 +28664,7 @@
         <v>178</v>
       </c>
       <c r="Q436" t="n">
-        <v>0.1072195888303848</v>
+        <v>0.10721958774575</v>
       </c>
       <c r="R436" t="inlineStr"/>
       <c r="S436" t="inlineStr"/>
@@ -28802,7 +28802,7 @@
         <v>187</v>
       </c>
       <c r="Q438" t="n">
-        <v>0.0977994512645663</v>
+        <v>0.09779945062755969</v>
       </c>
       <c r="R438" t="inlineStr"/>
       <c r="S438" t="inlineStr"/>
@@ -28873,7 +28873,7 @@
         <v>116</v>
       </c>
       <c r="Q439" t="n">
-        <v>0.1931409358142398</v>
+        <v>0.1931409352115853</v>
       </c>
       <c r="R439" t="inlineStr"/>
       <c r="S439" t="inlineStr"/>
@@ -29019,7 +29019,7 @@
         <v>158</v>
       </c>
       <c r="Q441" t="n">
-        <v>0.138531363066001</v>
+        <v>0.1385313621226884</v>
       </c>
       <c r="R441" t="inlineStr"/>
       <c r="S441" t="inlineStr"/>
@@ -29218,7 +29218,7 @@
         <v>128</v>
       </c>
       <c r="Q444" t="n">
-        <v>0.1780255812380377</v>
+        <v>0.1780255811948261</v>
       </c>
       <c r="R444" t="inlineStr"/>
       <c r="S444" t="inlineStr"/>
@@ -29285,7 +29285,7 @@
         <v>204</v>
       </c>
       <c r="Q445" t="n">
-        <v>0.0819291753926127</v>
+        <v>0.0819291751936594</v>
       </c>
       <c r="R445" t="inlineStr"/>
       <c r="S445" t="inlineStr"/>
@@ -29356,7 +29356,7 @@
         <v>282</v>
       </c>
       <c r="Q446" t="n">
-        <v>0.005548671419522</v>
+        <v>0.005548671434974</v>
       </c>
       <c r="R446" t="inlineStr"/>
       <c r="S446" t="inlineStr">
@@ -29484,7 +29484,7 @@
         <v>261</v>
       </c>
       <c r="Q448" t="n">
-        <v>0.026261927858936</v>
+        <v>0.0262619278602622</v>
       </c>
       <c r="R448" t="inlineStr"/>
       <c r="S448" t="inlineStr"/>
@@ -29555,7 +29555,7 @@
         <v>212</v>
       </c>
       <c r="Q449" t="n">
-        <v>0.0765677345914455</v>
+        <v>0.07656773429698729</v>
       </c>
       <c r="R449" t="inlineStr"/>
       <c r="S449" t="inlineStr"/>
@@ -29683,7 +29683,7 @@
         <v>67</v>
       </c>
       <c r="Q451" t="n">
-        <v>0.3230714467000144</v>
+        <v>0.3230714465913506</v>
       </c>
       <c r="R451" t="inlineStr"/>
       <c r="S451" t="inlineStr"/>
@@ -29754,7 +29754,7 @@
         <v>207</v>
       </c>
       <c r="Q452" t="n">
-        <v>0.0806726922545806</v>
+        <v>0.0806726918591051</v>
       </c>
       <c r="R452" t="inlineStr"/>
       <c r="S452" t="inlineStr"/>
@@ -29821,7 +29821,7 @@
         <v>121</v>
       </c>
       <c r="Q453" t="n">
-        <v>0.1873620199587518</v>
+        <v>0.1873620216892207</v>
       </c>
       <c r="R453" t="inlineStr"/>
       <c r="S453" t="inlineStr"/>
@@ -29892,7 +29892,7 @@
         <v>153</v>
       </c>
       <c r="Q454" t="n">
-        <v>0.1405164974587151</v>
+        <v>0.1405164927444923</v>
       </c>
       <c r="R454" t="inlineStr"/>
       <c r="S454" t="inlineStr"/>
@@ -30073,7 +30073,7 @@
         <v>97</v>
       </c>
       <c r="Q457" t="n">
-        <v>0.2458953673680066</v>
+        <v>0.2458953680628207</v>
       </c>
       <c r="R457" t="inlineStr"/>
       <c r="S457" t="inlineStr"/>
@@ -30144,7 +30144,7 @@
         <v>115</v>
       </c>
       <c r="Q458" t="n">
-        <v>0.1943648349511314</v>
+        <v>0.1943648353858606</v>
       </c>
       <c r="R458" t="inlineStr"/>
       <c r="S458" t="inlineStr"/>
@@ -30211,7 +30211,7 @@
         <v>62</v>
       </c>
       <c r="Q459" t="n">
-        <v>0.3476449030692279</v>
+        <v>0.3476449004457927</v>
       </c>
       <c r="R459" t="inlineStr"/>
       <c r="S459" t="inlineStr"/>
@@ -30349,7 +30349,7 @@
         <v>265</v>
       </c>
       <c r="Q461" t="n">
-        <v>0.0235318979273615</v>
+        <v>0.0235318979169753</v>
       </c>
       <c r="R461" t="inlineStr"/>
       <c r="S461" t="inlineStr"/>
@@ -30473,7 +30473,7 @@
         <v>232</v>
       </c>
       <c r="Q463" t="n">
-        <v>0.0652451465167162</v>
+        <v>0.0652451464467689</v>
       </c>
       <c r="R463" t="inlineStr"/>
       <c r="S463" t="inlineStr"/>
@@ -30601,7 +30601,7 @@
         <v>94</v>
       </c>
       <c r="Q465" t="n">
-        <v>0.2492573479165344</v>
+        <v>0.249257348266055</v>
       </c>
       <c r="R465" t="inlineStr"/>
       <c r="S465" t="inlineStr">
@@ -30814,7 +30814,7 @@
         <v>86</v>
       </c>
       <c r="Q468" t="n">
-        <v>0.2768393957228619</v>
+        <v>0.2768393968303386</v>
       </c>
       <c r="R468" t="inlineStr"/>
       <c r="S468" t="inlineStr"/>
@@ -30885,7 +30885,7 @@
         <v>99</v>
       </c>
       <c r="Q469" t="n">
-        <v>0.2449744204181269</v>
+        <v>0.244974419175426</v>
       </c>
       <c r="R469" t="inlineStr"/>
       <c r="S469" t="inlineStr"/>
@@ -30952,7 +30952,7 @@
         <v>136</v>
       </c>
       <c r="Q470" t="n">
-        <v>0.1627014038311406</v>
+        <v>0.1627014040699679</v>
       </c>
       <c r="R470" t="inlineStr"/>
       <c r="S470" t="inlineStr"/>
@@ -31023,7 +31023,7 @@
         <v>181</v>
       </c>
       <c r="Q471" t="n">
-        <v>0.1053753330613459</v>
+        <v>0.1053753327648039</v>
       </c>
       <c r="R471" t="inlineStr"/>
       <c r="S471" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
         <v>76</v>
       </c>
       <c r="Q472" t="n">
-        <v>0.296085873792237</v>
+        <v>0.2960858717362686</v>
       </c>
       <c r="R472" t="inlineStr"/>
       <c r="S472" t="inlineStr"/>
@@ -31165,7 +31165,7 @@
         <v>132</v>
       </c>
       <c r="Q473" t="n">
-        <v>0.1694634482227854</v>
+        <v>0.1694634484563496</v>
       </c>
       <c r="R473" t="inlineStr"/>
       <c r="S473" t="inlineStr"/>
@@ -31236,7 +31236,7 @@
         <v>73</v>
       </c>
       <c r="Q474" t="n">
-        <v>0.3015858678524386</v>
+        <v>0.301585866946738</v>
       </c>
       <c r="R474" t="inlineStr"/>
       <c r="S474" t="inlineStr"/>
@@ -31421,7 +31421,7 @@
         <v>225</v>
       </c>
       <c r="Q477" t="n">
-        <v>0.0679641603803862</v>
+        <v>0.0679641603360446</v>
       </c>
       <c r="R477" t="inlineStr"/>
       <c r="S477" t="inlineStr"/>
@@ -31549,7 +31549,7 @@
         <v>159</v>
       </c>
       <c r="Q479" t="n">
-        <v>0.1385279927987609</v>
+        <v>0.1385279921868029</v>
       </c>
       <c r="R479" t="inlineStr"/>
       <c r="S479" t="inlineStr"/>
@@ -31734,7 +31734,7 @@
         <v>194</v>
       </c>
       <c r="Q482" t="n">
-        <v>0.0913271090438386</v>
+        <v>0.0913271083009398</v>
       </c>
       <c r="R482" t="inlineStr"/>
       <c r="S482" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
         <v>149</v>
       </c>
       <c r="Q484" t="n">
-        <v>0.1465923640550767</v>
+        <v>0.1465923643965474</v>
       </c>
       <c r="R484" t="inlineStr"/>
       <c r="S484" t="inlineStr"/>
@@ -31990,7 +31990,7 @@
         <v>210</v>
       </c>
       <c r="Q486" t="n">
-        <v>0.077982623910039</v>
+        <v>0.0779826234157341</v>
       </c>
       <c r="R486" t="inlineStr"/>
       <c r="S486" t="inlineStr"/>
@@ -32232,7 +32232,7 @@
         <v>219</v>
       </c>
       <c r="Q490" t="n">
-        <v>0.0743105475993306</v>
+        <v>0.0743105475789269</v>
       </c>
       <c r="R490" t="inlineStr"/>
       <c r="S490" t="inlineStr"/>
@@ -32299,7 +32299,7 @@
         <v>114</v>
       </c>
       <c r="Q491" t="n">
-        <v>0.201061686448289</v>
+        <v>0.2010616854512954</v>
       </c>
       <c r="R491" t="inlineStr"/>
       <c r="S491" t="inlineStr"/>
@@ -32370,7 +32370,7 @@
         <v>157</v>
       </c>
       <c r="Q492" t="n">
-        <v>0.138630653955267</v>
+        <v>0.1386306574789947</v>
       </c>
       <c r="R492" t="inlineStr"/>
       <c r="S492" t="inlineStr"/>
@@ -32441,7 +32441,7 @@
         <v>64</v>
       </c>
       <c r="Q493" t="n">
-        <v>0.337075514072383</v>
+        <v>0.3370755130947255</v>
       </c>
       <c r="R493" t="inlineStr"/>
       <c r="S493" t="inlineStr"/>
@@ -32807,7 +32807,7 @@
         <v>271</v>
       </c>
       <c r="Q499" t="n">
-        <v>0.0175506450188389</v>
+        <v>0.0175506450188945</v>
       </c>
       <c r="R499" t="inlineStr"/>
       <c r="S499" t="inlineStr"/>
@@ -33291,7 +33291,7 @@
         <v>192</v>
       </c>
       <c r="Q507" t="n">
-        <v>0.09367680552210191</v>
+        <v>0.0936768053990623</v>
       </c>
       <c r="R507" t="inlineStr"/>
       <c r="S507" t="inlineStr"/>
@@ -33362,7 +33362,7 @@
         <v>129</v>
       </c>
       <c r="Q508" t="n">
-        <v>0.1757094803532384</v>
+        <v>0.1757094787449906</v>
       </c>
       <c r="R508" t="inlineStr"/>
       <c r="S508" t="inlineStr"/>
@@ -33433,7 +33433,7 @@
         <v>249</v>
       </c>
       <c r="Q509" t="n">
-        <v>0.0411389828607956</v>
+        <v>0.0411389826162849</v>
       </c>
       <c r="R509" t="inlineStr"/>
       <c r="S509" t="inlineStr"/>
@@ -33504,7 +33504,7 @@
         <v>87</v>
       </c>
       <c r="Q510" t="n">
-        <v>0.2697209009080312</v>
+        <v>0.2697209008190425</v>
       </c>
       <c r="R510" t="inlineStr"/>
       <c r="S510" t="inlineStr"/>
@@ -33689,7 +33689,7 @@
         <v>173</v>
       </c>
       <c r="Q513" t="n">
-        <v>0.1173256677180294</v>
+        <v>0.1173256670119973</v>
       </c>
       <c r="R513" t="inlineStr"/>
       <c r="S513" t="inlineStr"/>
@@ -33760,7 +33760,7 @@
         <v>215</v>
       </c>
       <c r="Q514" t="n">
-        <v>0.0753540098620796</v>
+        <v>0.0753540092661287</v>
       </c>
       <c r="R514" t="inlineStr"/>
       <c r="S514" t="inlineStr"/>
@@ -33831,7 +33831,7 @@
         <v>182</v>
       </c>
       <c r="Q515" t="n">
-        <v>0.1030287581695301</v>
+        <v>0.1030287559047355</v>
       </c>
       <c r="R515" t="inlineStr"/>
       <c r="S515" t="inlineStr"/>
@@ -33902,7 +33902,7 @@
         <v>96</v>
       </c>
       <c r="Q516" t="n">
-        <v>0.2473384922348745</v>
+        <v>0.2473384921530617</v>
       </c>
       <c r="R516" t="inlineStr"/>
       <c r="S516" t="inlineStr"/>
@@ -34040,7 +34040,7 @@
         <v>193</v>
       </c>
       <c r="Q518" t="n">
-        <v>0.09208494369697789</v>
+        <v>0.0920849446228016</v>
       </c>
       <c r="R518" t="inlineStr"/>
       <c r="S518" t="inlineStr"/>
@@ -34111,7 +34111,7 @@
         <v>112</v>
       </c>
       <c r="Q519" t="n">
-        <v>0.2063119366826543</v>
+        <v>0.2063119394060513</v>
       </c>
       <c r="R519" t="inlineStr"/>
       <c r="S519" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
         <v>240</v>
       </c>
       <c r="Q522" t="n">
-        <v>0.0566650216505879</v>
+        <v>0.0566650219443807</v>
       </c>
       <c r="R522" t="inlineStr"/>
       <c r="S522" t="inlineStr"/>
@@ -34381,7 +34381,7 @@
         <v>184</v>
       </c>
       <c r="Q523" t="n">
-        <v>0.1021459260291637</v>
+        <v>0.102145926029326</v>
       </c>
       <c r="R523" t="inlineStr"/>
       <c r="S523" t="inlineStr"/>
@@ -34452,7 +34452,7 @@
         <v>268</v>
       </c>
       <c r="Q524" t="n">
-        <v>0.0192505707720816</v>
+        <v>0.019250570681627</v>
       </c>
       <c r="R524" t="inlineStr"/>
       <c r="S524" t="inlineStr"/>
@@ -34523,7 +34523,7 @@
         <v>71</v>
       </c>
       <c r="Q525" t="n">
-        <v>0.3127512332561439</v>
+        <v>0.3127512329397147</v>
       </c>
       <c r="R525" t="inlineStr"/>
       <c r="S525" t="inlineStr"/>
@@ -34590,7 +34590,7 @@
         <v>123</v>
       </c>
       <c r="Q526" t="n">
-        <v>0.1862284116855768</v>
+        <v>0.1862284136412526</v>
       </c>
       <c r="R526" t="inlineStr"/>
       <c r="S526" t="inlineStr"/>
@@ -34661,7 +34661,7 @@
         <v>102</v>
       </c>
       <c r="Q527" t="n">
-        <v>0.2372985461520635</v>
+        <v>0.237298538023274</v>
       </c>
       <c r="R527" t="inlineStr"/>
       <c r="S527" t="inlineStr"/>
@@ -34803,7 +34803,7 @@
         <v>89</v>
       </c>
       <c r="Q529" t="n">
-        <v>0.2662596818352701</v>
+        <v>0.2662596864344671</v>
       </c>
       <c r="R529" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>131</v>
       </c>
       <c r="Q530" t="n">
-        <v>0.1731717319971636</v>
+        <v>0.173171732063121</v>
       </c>
       <c r="R530" t="inlineStr"/>
       <c r="S530" t="inlineStr"/>
@@ -34953,7 +34953,7 @@
         <v>63</v>
       </c>
       <c r="Q531" t="n">
-        <v>0.3453992968560903</v>
+        <v>0.345399298867179</v>
       </c>
       <c r="R531" t="inlineStr"/>
       <c r="S531" t="inlineStr"/>
@@ -35024,7 +35024,7 @@
         <v>145</v>
       </c>
       <c r="Q532" t="n">
-        <v>0.1518432337423133</v>
+        <v>0.151843234871835</v>
       </c>
       <c r="R532" t="inlineStr"/>
       <c r="S532" t="inlineStr"/>
@@ -35095,7 +35095,7 @@
         <v>206</v>
       </c>
       <c r="Q533" t="n">
-        <v>0.0806990752111956</v>
+        <v>0.0806990758127737</v>
       </c>
       <c r="R533" t="inlineStr"/>
       <c r="S533" t="inlineStr"/>
@@ -35166,7 +35166,7 @@
         <v>118</v>
       </c>
       <c r="Q534" t="n">
-        <v>0.1907238515976559</v>
+        <v>0.1907238530404656</v>
       </c>
       <c r="R534" t="inlineStr"/>
       <c r="S534" t="inlineStr"/>
@@ -35237,7 +35237,7 @@
         <v>254</v>
       </c>
       <c r="Q535" t="n">
-        <v>0.0347291478441294</v>
+        <v>0.034729147869885</v>
       </c>
       <c r="R535" t="inlineStr"/>
       <c r="S535" t="inlineStr"/>
@@ -35379,7 +35379,7 @@
         <v>239</v>
       </c>
       <c r="Q537" t="n">
-        <v>0.0576338045515062</v>
+        <v>0.0576338050170916</v>
       </c>
       <c r="R537" t="inlineStr"/>
       <c r="S537" t="inlineStr"/>
@@ -35521,7 +35521,7 @@
         <v>218</v>
       </c>
       <c r="Q539" t="n">
-        <v>0.0747194172238712</v>
+        <v>0.0747194172284599</v>
       </c>
       <c r="R539" t="inlineStr"/>
       <c r="S539" t="inlineStr"/>
@@ -35663,7 +35663,7 @@
         <v>198</v>
       </c>
       <c r="Q541" t="n">
-        <v>0.0856255835115789</v>
+        <v>0.08562558450385881</v>
       </c>
       <c r="R541" t="inlineStr"/>
       <c r="S541" t="inlineStr"/>
@@ -35734,7 +35734,7 @@
         <v>185</v>
       </c>
       <c r="Q542" t="n">
-        <v>0.101334922074056</v>
+        <v>0.1013349225335817</v>
       </c>
       <c r="R542" t="inlineStr"/>
       <c r="S542" t="inlineStr"/>
@@ -35876,7 +35876,7 @@
         <v>245</v>
       </c>
       <c r="Q544" t="n">
-        <v>0.0463521265005554</v>
+        <v>0.0463521270619127</v>
       </c>
       <c r="R544" t="inlineStr"/>
       <c r="S544" t="inlineStr"/>
@@ -35947,7 +35947,7 @@
         <v>259</v>
       </c>
       <c r="Q545" t="n">
-        <v>0.0288976473724475</v>
+        <v>0.0288976474139661</v>
       </c>
       <c r="R545" t="inlineStr"/>
       <c r="S545" t="inlineStr"/>
@@ -36018,7 +36018,7 @@
         <v>168</v>
       </c>
       <c r="Q546" t="n">
-        <v>0.1256378592876022</v>
+        <v>0.1256378601484289</v>
       </c>
       <c r="R546" t="inlineStr"/>
       <c r="S546" t="inlineStr"/>
@@ -36678,7 +36678,7 @@
         <v>163</v>
       </c>
       <c r="Q556" t="n">
-        <v>0.1355131278345899</v>
+        <v>0.1355131279515838</v>
       </c>
       <c r="R556" t="inlineStr"/>
       <c r="S556" t="inlineStr"/>
@@ -37205,7 +37205,7 @@
         <v>247</v>
       </c>
       <c r="Q565" t="n">
-        <v>0.0451915622436144</v>
+        <v>0.0451915621107183</v>
       </c>
       <c r="R565" t="inlineStr"/>
       <c r="S565" t="inlineStr"/>
@@ -37333,7 +37333,7 @@
         <v>81</v>
       </c>
       <c r="Q567" t="n">
-        <v>0.2914386651374229</v>
+        <v>0.2914386650696634</v>
       </c>
       <c r="R567" t="inlineStr"/>
       <c r="S567" t="inlineStr"/>
@@ -37404,7 +37404,7 @@
         <v>139</v>
       </c>
       <c r="Q568" t="n">
-        <v>0.1596449439516595</v>
+        <v>0.1596449444341947</v>
       </c>
       <c r="R568" t="inlineStr"/>
       <c r="S568" t="inlineStr"/>
@@ -37609,7 +37609,7 @@
         <v>248</v>
       </c>
       <c r="Q571" t="n">
-        <v>0.0440145876976862</v>
+        <v>0.0440145874194997</v>
       </c>
       <c r="R571" t="inlineStr"/>
       <c r="S571" t="inlineStr"/>
@@ -37680,7 +37680,7 @@
         <v>273</v>
       </c>
       <c r="Q572" t="n">
-        <v>0.0151811850298901</v>
+        <v>0.0151811849810569</v>
       </c>
       <c r="R572" t="inlineStr"/>
       <c r="S572" t="inlineStr"/>
@@ -38127,7 +38127,7 @@
         <v>190</v>
       </c>
       <c r="Q579" t="n">
-        <v>0.096704997675365</v>
+        <v>0.0967049982362356</v>
       </c>
       <c r="R579" t="inlineStr"/>
       <c r="S579" t="inlineStr"/>
@@ -38255,7 +38255,7 @@
         <v>266</v>
       </c>
       <c r="Q581" t="n">
-        <v>0.02219788394318</v>
+        <v>0.0221978839975276</v>
       </c>
       <c r="R581" t="inlineStr"/>
       <c r="S581" t="inlineStr"/>
@@ -38326,7 +38326,7 @@
         <v>176</v>
       </c>
       <c r="Q582" t="n">
-        <v>0.113590097551741</v>
+        <v>0.1135900977478483</v>
       </c>
       <c r="R582" t="inlineStr"/>
       <c r="S582" t="inlineStr"/>
@@ -38525,7 +38525,7 @@
         <v>195</v>
       </c>
       <c r="Q585" t="n">
-        <v>0.0883472094946131</v>
+        <v>0.08834720974877849</v>
       </c>
       <c r="R585" t="inlineStr"/>
       <c r="S585" t="inlineStr"/>
@@ -38781,7 +38781,7 @@
         <v>155</v>
       </c>
       <c r="Q589" t="n">
-        <v>0.1396996326834606</v>
+        <v>0.1396996331391438</v>
       </c>
       <c r="R589" t="inlineStr"/>
       <c r="S589" t="inlineStr"/>
@@ -38852,7 +38852,7 @@
         <v>167</v>
       </c>
       <c r="Q590" t="n">
-        <v>0.1257618505741137</v>
+        <v>0.1257618508417461</v>
       </c>
       <c r="R590" t="inlineStr"/>
       <c r="S590" t="inlineStr"/>
@@ -38923,7 +38923,7 @@
         <v>251</v>
       </c>
       <c r="Q591" t="n">
-        <v>0.0376778506200125</v>
+        <v>0.0376778504670044</v>
       </c>
       <c r="R591" t="inlineStr"/>
       <c r="S591" t="inlineStr"/>
@@ -38994,7 +38994,7 @@
         <v>241</v>
       </c>
       <c r="Q592" t="n">
-        <v>0.0546734455919884</v>
+        <v>0.0546734459412497</v>
       </c>
       <c r="R592" t="inlineStr"/>
       <c r="S592" t="inlineStr"/>
@@ -39250,7 +39250,7 @@
         <v>260</v>
       </c>
       <c r="Q596" t="n">
-        <v>0.0287638861829401</v>
+        <v>0.0287638861947618</v>
       </c>
       <c r="R596" t="inlineStr"/>
       <c r="S596" t="inlineStr"/>
@@ -39862,7 +39862,7 @@
         <v>74</v>
       </c>
       <c r="Q606" t="n">
-        <v>0.3009598605665321</v>
+        <v>0.3009598608937349</v>
       </c>
       <c r="R606" t="inlineStr"/>
       <c r="S606" t="inlineStr"/>
@@ -39990,7 +39990,7 @@
         <v>214</v>
       </c>
       <c r="Q608" t="n">
-        <v>0.0755991041030822</v>
+        <v>0.0755991042067778</v>
       </c>
       <c r="R608" t="inlineStr"/>
       <c r="S608" t="inlineStr"/>
@@ -40057,7 +40057,7 @@
         <v>258</v>
       </c>
       <c r="Q609" t="n">
-        <v>0.0291250391668336</v>
+        <v>0.0291250390900226</v>
       </c>
       <c r="R609" t="inlineStr"/>
       <c r="S609" t="inlineStr"/>
@@ -40128,7 +40128,7 @@
         <v>133</v>
       </c>
       <c r="Q610" t="n">
-        <v>0.1693370981143288</v>
+        <v>0.1693370974912838</v>
       </c>
       <c r="R610" t="inlineStr"/>
       <c r="S610" t="inlineStr"/>
@@ -40199,7 +40199,7 @@
         <v>51</v>
       </c>
       <c r="Q611" t="n">
-        <v>0.403069786815397</v>
+        <v>0.4030697872878174</v>
       </c>
       <c r="R611" t="inlineStr"/>
       <c r="S611" t="inlineStr"/>
@@ -40327,7 +40327,7 @@
         <v>165</v>
       </c>
       <c r="Q613" t="n">
-        <v>0.1291983064427726</v>
+        <v>0.1291983064522342</v>
       </c>
       <c r="R613" t="inlineStr"/>
       <c r="S613" t="inlineStr"/>
@@ -40398,7 +40398,7 @@
         <v>171</v>
       </c>
       <c r="Q614" t="n">
-        <v>0.1181148920953586</v>
+        <v>0.1181148923334288</v>
       </c>
       <c r="R614" t="inlineStr"/>
       <c r="S614" t="inlineStr"/>
@@ -40583,7 +40583,7 @@
         <v>216</v>
       </c>
       <c r="Q617" t="n">
-        <v>0.0752790370236734</v>
+        <v>0.0752790370814214</v>
       </c>
       <c r="R617" t="inlineStr"/>
       <c r="S617" t="inlineStr"/>
@@ -40711,7 +40711,7 @@
         <v>231</v>
       </c>
       <c r="Q619" t="n">
-        <v>0.0658087163960762</v>
+        <v>0.06580871670546611</v>
       </c>
       <c r="R619" t="inlineStr"/>
       <c r="S619" t="inlineStr"/>
@@ -40782,7 +40782,7 @@
         <v>238</v>
       </c>
       <c r="Q620" t="n">
-        <v>0.0583611294448093</v>
+        <v>0.0583611289704404</v>
       </c>
       <c r="R620" t="inlineStr"/>
       <c r="S620" t="inlineStr"/>
@@ -40981,7 +40981,7 @@
         <v>200</v>
       </c>
       <c r="Q623" t="n">
-        <v>0.0842335701936059</v>
+        <v>0.08423356914425879</v>
       </c>
       <c r="R623" t="inlineStr"/>
       <c r="S623" t="inlineStr"/>
@@ -41052,7 +41052,7 @@
         <v>11</v>
       </c>
       <c r="Q624" t="n">
-        <v>1.128056554324097</v>
+        <v>1.128056553111823</v>
       </c>
       <c r="R624" t="inlineStr"/>
       <c r="S624" t="inlineStr"/>
@@ -41123,7 +41123,7 @@
         <v>269</v>
       </c>
       <c r="Q625" t="n">
-        <v>0.0181864593511464</v>
+        <v>0.0181864595055796</v>
       </c>
       <c r="R625" t="inlineStr"/>
       <c r="S625" t="inlineStr"/>
@@ -41194,7 +41194,7 @@
         <v>110</v>
       </c>
       <c r="Q626" t="n">
-        <v>0.2179315828758856</v>
+        <v>0.2179315812532847</v>
       </c>
       <c r="R626" t="inlineStr"/>
       <c r="S626" t="inlineStr"/>
@@ -41265,7 +41265,7 @@
         <v>137</v>
       </c>
       <c r="Q627" t="n">
-        <v>0.1624315873032645</v>
+        <v>0.1624315874369763</v>
       </c>
       <c r="R627" t="inlineStr"/>
       <c r="S627" t="inlineStr"/>
@@ -41336,7 +41336,7 @@
         <v>91</v>
       </c>
       <c r="Q628" t="n">
-        <v>0.2612608738288006</v>
+        <v>0.2612608733556462</v>
       </c>
       <c r="R628" t="inlineStr"/>
       <c r="S628" t="inlineStr"/>
@@ -41407,7 +41407,7 @@
         <v>134</v>
       </c>
       <c r="Q629" t="n">
-        <v>0.1690928723903345</v>
+        <v>0.169092871564394</v>
       </c>
       <c r="R629" t="inlineStr"/>
       <c r="S629" t="inlineStr"/>
@@ -41478,7 +41478,7 @@
         <v>227</v>
       </c>
       <c r="Q630" t="n">
-        <v>0.0676257319009077</v>
+        <v>0.0676257322124774</v>
       </c>
       <c r="R630" t="inlineStr"/>
       <c r="S630" t="inlineStr"/>
@@ -41687,7 +41687,7 @@
         <v>41</v>
       </c>
       <c r="Q633" t="n">
-        <v>0.4819144059178167</v>
+        <v>0.481914403524861</v>
       </c>
       <c r="R633" t="inlineStr"/>
       <c r="S633" t="inlineStr"/>
@@ -41754,7 +41754,7 @@
         <v>93</v>
       </c>
       <c r="Q634" t="n">
-        <v>0.2500687755865019</v>
+        <v>0.2500687747465059</v>
       </c>
       <c r="R634" t="inlineStr"/>
       <c r="S634" t="inlineStr"/>
@@ -41953,7 +41953,7 @@
         <v>279</v>
       </c>
       <c r="Q637" t="n">
-        <v>0.0096271406732358</v>
+        <v>0.009627140665729001</v>
       </c>
       <c r="R637" t="inlineStr"/>
       <c r="S637" t="inlineStr"/>
@@ -42024,7 +42024,7 @@
         <v>257</v>
       </c>
       <c r="Q638" t="n">
-        <v>0.0300510154764377</v>
+        <v>0.0300510154492188</v>
       </c>
       <c r="R638" t="inlineStr"/>
       <c r="S638" t="inlineStr"/>
@@ -42095,7 +42095,7 @@
         <v>229</v>
       </c>
       <c r="Q639" t="n">
-        <v>0.0668342432701631</v>
+        <v>0.0668342434009984</v>
       </c>
       <c r="R639" t="inlineStr"/>
       <c r="S639" t="inlineStr"/>
@@ -42223,7 +42223,7 @@
         <v>281</v>
       </c>
       <c r="Q641" t="n">
-        <v>0.0078485637150721</v>
+        <v>0.007848563710024299</v>
       </c>
       <c r="R641" t="inlineStr"/>
       <c r="S641" t="inlineStr"/>
@@ -42294,7 +42294,7 @@
         <v>83</v>
       </c>
       <c r="Q642" t="n">
-        <v>0.2843659083005886</v>
+        <v>0.2843659090098198</v>
       </c>
       <c r="R642" t="inlineStr"/>
       <c r="S642" t="inlineStr"/>
@@ -42365,7 +42365,7 @@
         <v>108</v>
       </c>
       <c r="Q643" t="n">
-        <v>0.2224843674390065</v>
+        <v>0.2224843685152405</v>
       </c>
       <c r="R643" t="inlineStr"/>
       <c r="S643" t="inlineStr"/>
@@ -42436,7 +42436,7 @@
         <v>197</v>
       </c>
       <c r="Q644" t="n">
-        <v>0.08649926423334291</v>
+        <v>0.0864992646664024</v>
       </c>
       <c r="R644" t="inlineStr"/>
       <c r="S644" t="inlineStr"/>
@@ -42578,7 +42578,7 @@
         <v>111</v>
       </c>
       <c r="Q646" t="n">
-        <v>0.2068253690971373</v>
+        <v>0.2068253683462282</v>
       </c>
       <c r="R646" t="inlineStr"/>
       <c r="S646" t="inlineStr"/>
@@ -42649,7 +42649,7 @@
         <v>70</v>
       </c>
       <c r="Q647" t="n">
-        <v>0.3177488903595923</v>
+        <v>0.3177488903567858</v>
       </c>
       <c r="R647" t="inlineStr"/>
       <c r="S647" t="inlineStr"/>
@@ -42720,7 +42720,7 @@
         <v>213</v>
       </c>
       <c r="Q648" t="n">
-        <v>0.0758838494979911</v>
+        <v>0.0758838492508879</v>
       </c>
       <c r="R648" t="inlineStr"/>
       <c r="S648" t="inlineStr"/>
@@ -42791,7 +42791,7 @@
         <v>144</v>
       </c>
       <c r="Q649" t="n">
-        <v>0.1524631752926004</v>
+        <v>0.152463175327636</v>
       </c>
       <c r="R649" t="inlineStr"/>
       <c r="S649" t="inlineStr"/>
@@ -42862,7 +42862,7 @@
         <v>143</v>
       </c>
       <c r="Q650" t="n">
-        <v>0.1566409634091377</v>
+        <v>0.156640965106948</v>
       </c>
       <c r="R650" t="inlineStr"/>
       <c r="S650" t="inlineStr"/>
@@ -43104,7 +43104,7 @@
         <v>236</v>
       </c>
       <c r="Q654" t="n">
-        <v>0.0592101211106404</v>
+        <v>0.0592101205162679</v>
       </c>
       <c r="R654" t="inlineStr"/>
       <c r="S654" t="inlineStr"/>
@@ -43346,7 +43346,7 @@
         <v>275</v>
       </c>
       <c r="Q658" t="n">
-        <v>0.0117804912169294</v>
+        <v>0.0117804912145817</v>
       </c>
       <c r="R658" t="inlineStr"/>
       <c r="S658" t="inlineStr"/>
@@ -43612,7 +43612,7 @@
         <v>264</v>
       </c>
       <c r="Q662" t="n">
-        <v>0.0235473866188571</v>
+        <v>0.0235473866647673</v>
       </c>
       <c r="R662" t="inlineStr"/>
       <c r="S662" t="inlineStr">
@@ -45054,30 +45054,34 @@
       </c>
       <c r="I687" t="inlineStr">
         <is>
+          <t>(비활성화)</t>
+        </is>
+      </c>
+      <c r="J687" t="b">
+        <v>1</v>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>중복 통합(비활성화)</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>#853과 같은 의도(죽는 시점·방식) 중복</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>중복 통합(#853) · 신규 S013(Aron 36문항)과 주제 겹침</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
           <t>100살까지 사는 것과 건강하게 80살까지 사는 것 중 뭐가 더 나은가요?</t>
         </is>
       </c>
-      <c r="J687" t="b">
-        <v>1</v>
-      </c>
-      <c r="K687" t="inlineStr">
-        <is>
-          <t>재작성</t>
-        </is>
-      </c>
-      <c r="L687" t="inlineStr">
-        <is>
-          <t>#853과 같은 의도(죽는 시점·방식) 중복</t>
-        </is>
-      </c>
-      <c r="M687" t="inlineStr">
-        <is>
-          <t>중복 해소 → 다른 각도의 양자택일</t>
-        </is>
-      </c>
-      <c r="N687" t="inlineStr"/>
       <c r="O687" t="n">
-        <v>-5.704492715057147</v>
+        <v>0</v>
       </c>
       <c r="P687" t="n">
         <v>351</v>
@@ -45264,7 +45268,7 @@
         <v>242</v>
       </c>
       <c r="Q690" t="n">
-        <v>0.0526795752072951</v>
+        <v>0.0526795752080927</v>
       </c>
       <c r="R690" t="inlineStr"/>
       <c r="S690" t="inlineStr"/>
@@ -45734,7 +45738,7 @@
         <v>172</v>
       </c>
       <c r="Q698" t="n">
-        <v>0.1174078878647791</v>
+        <v>0.1174078878093762</v>
       </c>
       <c r="R698" t="inlineStr"/>
       <c r="S698" t="inlineStr"/>
@@ -48526,7 +48530,7 @@
         <v>235</v>
       </c>
       <c r="Q746" t="n">
-        <v>0.0614316358853387</v>
+        <v>0.061431635970571</v>
       </c>
       <c r="R746" t="inlineStr"/>
       <c r="S746" t="inlineStr"/>
@@ -48711,7 +48715,7 @@
         <v>255</v>
       </c>
       <c r="Q749" t="n">
-        <v>0.0343081282459821</v>
+        <v>0.034308128156838</v>
       </c>
       <c r="R749" t="inlineStr"/>
       <c r="S749" t="inlineStr"/>
@@ -48896,7 +48900,7 @@
         <v>246</v>
       </c>
       <c r="Q752" t="n">
-        <v>0.0456713533827165</v>
+        <v>0.0456713534194809</v>
       </c>
       <c r="R752" t="inlineStr"/>
       <c r="S752" t="inlineStr"/>
@@ -49138,7 +49142,7 @@
         <v>223</v>
       </c>
       <c r="Q756" t="n">
-        <v>0.0718934098385287</v>
+        <v>0.0718934099020183</v>
       </c>
       <c r="R756" t="inlineStr"/>
       <c r="S756" t="inlineStr"/>
@@ -51649,7 +51653,7 @@
         <v>191</v>
       </c>
       <c r="Q799" t="n">
-        <v>0.0937425578999284</v>
+        <v>0.093742557992453</v>
       </c>
       <c r="R799" t="inlineStr"/>
       <c r="S799" t="inlineStr"/>
@@ -51891,7 +51895,7 @@
         <v>151</v>
       </c>
       <c r="Q803" t="n">
-        <v>0.1410664284728315</v>
+        <v>0.1410664286786173</v>
       </c>
       <c r="R803" t="inlineStr"/>
       <c r="S803" t="inlineStr"/>
@@ -52190,7 +52194,7 @@
         <v>253</v>
       </c>
       <c r="Q808" t="n">
-        <v>0.0373003260338959</v>
+        <v>0.0373003260791848</v>
       </c>
       <c r="R808" t="inlineStr"/>
       <c r="S808" t="inlineStr"/>
@@ -53362,7 +53366,7 @@
         <v>135</v>
       </c>
       <c r="Q828" t="n">
-        <v>0.1632608861421532</v>
+        <v>0.1632608862248837</v>
       </c>
       <c r="R828" t="inlineStr"/>
       <c r="S828" t="inlineStr"/>
@@ -56065,7 +56069,7 @@
         <v>272</v>
       </c>
       <c r="Q875" t="n">
-        <v>0.0153991068616709</v>
+        <v>0.0153991068812722</v>
       </c>
       <c r="R875" t="inlineStr"/>
       <c r="S875" t="inlineStr"/>
@@ -56136,7 +56140,7 @@
         <v>278</v>
       </c>
       <c r="Q876" t="n">
-        <v>0.009663534114362</v>
+        <v>0.009663534128441899</v>
       </c>
       <c r="R876" t="inlineStr"/>
       <c r="S876" t="inlineStr"/>
@@ -56339,7 +56343,7 @@
         <v>45</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4547422795802848</v>
+        <v>0.4547422827072897</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
@@ -56410,7 +56414,7 @@
         <v>98</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2458441829848769</v>
+        <v>0.2458441855728337</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
@@ -56481,7 +56485,7 @@
         <v>46</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4502808655649432</v>
+        <v>0.4502808655268764</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
@@ -56552,7 +56556,7 @@
         <v>78</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2952355501391798</v>
+        <v>0.2952355448848513</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
@@ -56623,7 +56627,7 @@
         <v>100</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2378700107126246</v>
+        <v>0.2378700102547778</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
@@ -56765,7 +56769,7 @@
         <v>146</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1500068943811977</v>
+        <v>0.1500068961205726</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
@@ -56836,7 +56840,7 @@
         <v>39</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4842197466555238</v>
+        <v>0.4842197424207495</v>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -56903,7 +56907,7 @@
         <v>57</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.377145420176954</v>
+        <v>0.3771454261577982</v>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -56974,7 +56978,7 @@
         <v>106</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2241666282526584</v>
+        <v>0.2241666297228008</v>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -57116,7 +57120,7 @@
         <v>175</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1139434377582921</v>
+        <v>0.1139434375512308</v>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -57333,7 +57337,7 @@
         <v>54</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3834105333822548</v>
+        <v>0.3834105314086291</v>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -57471,7 +57475,7 @@
         <v>53</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.3835448518039157</v>
+        <v>0.3835448489416398</v>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -57542,7 +57546,7 @@
         <v>61</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3505904872967197</v>
+        <v>0.3505904854216243</v>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -57613,7 +57617,7 @@
         <v>80</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2933997665717098</v>
+        <v>0.293399766322991</v>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -57755,7 +57759,7 @@
         <v>17</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.890957956571074</v>
+        <v>0.8909579539612801</v>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
@@ -57826,7 +57830,7 @@
         <v>25</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.6148815606279704</v>
+        <v>0.6148815609814982</v>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -57897,7 +57901,7 @@
         <v>177</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1072784959373221</v>
+        <v>0.1072784961265131</v>
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
@@ -57968,7 +57972,7 @@
         <v>107</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2238903561463012</v>
+        <v>0.223890354536146</v>
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
@@ -58039,7 +58043,7 @@
         <v>22</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.7197976797460508</v>
+        <v>0.7197976763994859</v>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
@@ -58110,7 +58114,7 @@
         <v>60</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.3524293163366528</v>
+        <v>0.3524293192803396</v>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
@@ -58181,7 +58185,7 @@
         <v>150</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1447818810279481</v>
+        <v>0.1447818809615887</v>
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
@@ -58252,7 +58256,7 @@
         <v>21</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.792561416095188</v>
+        <v>0.7925614174428081</v>
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
@@ -58323,7 +58327,7 @@
         <v>34</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.538021365436351</v>
+        <v>0.5380213657727635</v>
       </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
@@ -58394,7 +58398,7 @@
         <v>14</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9619489795446871</v>
+        <v>0.9619489740657668</v>
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
@@ -58465,7 +58469,7 @@
         <v>48</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.4256712508539423</v>
+        <v>0.4256712509831923</v>
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -58607,7 +58611,7 @@
         <v>220</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.07383368994968489</v>
+        <v>0.07383368915694639</v>
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
@@ -58678,7 +58682,7 @@
         <v>55</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3796124968690004</v>
+        <v>0.3796124956301423</v>
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -58749,7 +58753,7 @@
         <v>50</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.4237762756483722</v>
+        <v>0.4237762754376256</v>
       </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -58820,7 +58824,7 @@
         <v>13</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9990980208916074</v>
+        <v>0.9990980198416328</v>
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -58891,7 +58895,7 @@
         <v>27</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.6038899530473893</v>
+        <v>0.6038899553065709</v>
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -58962,7 +58966,7 @@
         <v>174</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.1141709208919321</v>
+        <v>0.114170921614333</v>
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
@@ -59033,7 +59037,7 @@
         <v>154</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.1403365387018615</v>
+        <v>0.1403365386805624</v>
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -59104,7 +59108,7 @@
         <v>90</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.2658867873580479</v>
+        <v>0.2658867831585775</v>
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -59175,7 +59179,7 @@
         <v>287</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.0017276241512694</v>
+        <v>0.0017276241473718</v>
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -59246,7 +59250,7 @@
         <v>267</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.0193445398173798</v>
+        <v>0.0193445397733174</v>
       </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -59317,7 +59321,7 @@
         <v>30</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.5723008783133967</v>
+        <v>0.5723008773777398</v>
       </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
@@ -59388,7 +59392,7 @@
         <v>243</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.050173175463388</v>
+        <v>0.0501731751374618</v>
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
@@ -59459,7 +59463,7 @@
         <v>49</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.4241336509710668</v>
+        <v>0.4241336473150646</v>
       </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -59530,7 +59534,7 @@
         <v>69</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.3189343991839057</v>
+        <v>0.3189343995726886</v>
       </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
@@ -59601,7 +59605,7 @@
         <v>244</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.0481432549890464</v>
+        <v>0.0481432550528766</v>
       </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -59814,7 +59818,7 @@
         <v>203</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.0825546771768009</v>
+        <v>0.0825546766316614</v>
       </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -59956,7 +59960,7 @@
         <v>156</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.1392376426816677</v>
+        <v>0.1392376422468438</v>
       </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
@@ -60094,7 +60098,7 @@
         <v>208</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.0801809548459565</v>
+        <v>0.08018095465931969</v>
       </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -60161,7 +60165,7 @@
         <v>26</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.6119960197306289</v>
+        <v>0.6119960167838771</v>
       </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -60232,7 +60236,7 @@
         <v>224</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.06930730229210121</v>
+        <v>0.0693073021656844</v>
       </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
@@ -60303,7 +60307,7 @@
         <v>33</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.5571099705686849</v>
+        <v>0.5571099671060507</v>
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -60374,7 +60378,7 @@
         <v>127</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.179708830224044</v>
+        <v>0.1797088297467197</v>
       </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
@@ -60445,7 +60449,7 @@
         <v>95</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.2479276168587277</v>
+        <v>0.2479276167380216</v>
       </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -60516,7 +60520,7 @@
         <v>119</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.1906176010839483</v>
+        <v>0.190617602778101</v>
       </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
@@ -60587,7 +60591,7 @@
         <v>68</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.3215107754217839</v>
+        <v>0.3215107748327863</v>
       </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
@@ -60658,7 +60662,7 @@
         <v>113</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.2036146719632358</v>
+        <v>0.2036146721281323</v>
       </c>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
@@ -60729,7 +60733,7 @@
         <v>164</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.1301966711031801</v>
+        <v>0.1301966712260819</v>
       </c>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
@@ -60800,7 +60804,7 @@
         <v>66</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.3275821210119635</v>
+        <v>0.3275821219554654</v>
       </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
@@ -60871,7 +60875,7 @@
         <v>79</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.2942367290838963</v>
+        <v>0.2942367286049314</v>
       </c>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
@@ -60942,7 +60946,7 @@
         <v>59</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.363198427573286</v>
+        <v>0.3631984251391726</v>
       </c>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
@@ -61013,7 +61017,7 @@
         <v>179</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.1071315123390006</v>
+        <v>0.1071315122600101</v>
       </c>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
@@ -61084,7 +61088,7 @@
         <v>234</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.0635033219480422</v>
+        <v>0.0635033217975645</v>
       </c>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
@@ -61226,7 +61230,7 @@
         <v>109</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.2190980108249647</v>
+        <v>0.2190980103425579</v>
       </c>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
@@ -61297,7 +61301,7 @@
         <v>103</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.2285397966876771</v>
+        <v>0.2285397961866024</v>
       </c>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
@@ -61368,7 +61372,7 @@
         <v>228</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.0673547693325488</v>
+        <v>0.06735476911548249</v>
       </c>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
@@ -61510,7 +61514,7 @@
         <v>88</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.2696155517040787</v>
+        <v>0.2696155518392379</v>
       </c>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
@@ -61652,7 +61656,7 @@
         <v>141</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.158086383108305</v>
+        <v>0.158086382300763</v>
       </c>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
@@ -61723,7 +61727,7 @@
         <v>230</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.06612873571937621</v>
+        <v>0.06612873594133151</v>
       </c>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
@@ -61865,7 +61869,7 @@
         <v>189</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.09719655074945049</v>
+        <v>0.09719655157010031</v>
       </c>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
@@ -62007,7 +62011,7 @@
         <v>152</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.1409626221306283</v>
+        <v>0.1409626206519375</v>
       </c>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
@@ -62220,7 +62224,7 @@
         <v>202</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.0827757435141263</v>
+        <v>0.08277574395294821</v>
       </c>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr"/>
@@ -62291,7 +62295,7 @@
         <v>160</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.1375912581031854</v>
+        <v>0.1375912580325612</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
@@ -62504,7 +62508,7 @@
         <v>169</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.1249721423949838</v>
+        <v>0.1249721423551462</v>
       </c>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr"/>
@@ -62717,7 +62721,7 @@
         <v>256</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.0326479158368244</v>
+        <v>0.032647915462264</v>
       </c>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr"/>
@@ -62788,7 +62792,7 @@
         <v>211</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.0767586737396341</v>
+        <v>0.0767586738019542</v>
       </c>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr"/>
@@ -62930,7 +62934,7 @@
         <v>104</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.227248354773365</v>
+        <v>0.2272483545663617</v>
       </c>
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr"/>
@@ -63001,7 +63005,7 @@
         <v>222</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.0724339413999564</v>
+        <v>0.0724339414044214</v>
       </c>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr"/>
@@ -63072,7 +63076,7 @@
         <v>252</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.0375527686976297</v>
+        <v>0.0375527691823863</v>
       </c>
       <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr"/>
@@ -63143,7 +63147,7 @@
         <v>125</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.1832889705191899</v>
+        <v>0.1832889687857333</v>
       </c>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr"/>
@@ -63356,7 +63360,7 @@
         <v>199</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.0852199679854896</v>
+        <v>0.08521996719658539</v>
       </c>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr"/>
@@ -63498,7 +63502,7 @@
         <v>283</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.0053799651642695</v>
+        <v>0.0053799652033142</v>
       </c>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
@@ -63569,7 +63573,7 @@
         <v>286</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.0018666987473211</v>
+        <v>0.0018666987493512</v>
       </c>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
@@ -63782,7 +63786,7 @@
         <v>274</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.0122052657109853</v>
+        <v>0.0122052657630616</v>
       </c>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr"/>
@@ -63991,7 +63995,7 @@
         <v>166</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.1271754709459482</v>
+        <v>0.127175471632148</v>
       </c>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
@@ -64058,7 +64062,7 @@
         <v>120</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.1891131987801722</v>
+        <v>0.1891131987750259</v>
       </c>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr"/>
@@ -64129,7 +64133,7 @@
         <v>117</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.1918969139526298</v>
+        <v>0.1918969138800904</v>
       </c>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr"/>
@@ -64200,7 +64204,7 @@
         <v>82</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.2857281937139234</v>
+        <v>0.2857281935592242</v>
       </c>
       <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
@@ -64271,7 +64275,7 @@
         <v>277</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.010312248775314</v>
+        <v>0.0103122488576046</v>
       </c>
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr"/>
@@ -64413,7 +64417,7 @@
         <v>162</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.1370474516710556</v>
+        <v>0.1370474516405825</v>
       </c>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr"/>
@@ -64480,7 +64484,7 @@
         <v>138</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.1618642019419722</v>
+        <v>0.1618642026020011</v>
       </c>
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr"/>
@@ -64551,7 +64555,7 @@
         <v>183</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.1025553819711048</v>
+        <v>0.1025553820530929</v>
       </c>
       <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr"/>
@@ -64622,7 +64626,7 @@
         <v>285</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.0034161649124316</v>
+        <v>0.0034161649279003</v>
       </c>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr"/>
@@ -64693,7 +64697,7 @@
         <v>276</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.0117431250808903</v>
+        <v>0.0117431250742536</v>
       </c>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr"/>
@@ -64764,7 +64768,7 @@
         <v>147</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.1482861990191183</v>
+        <v>0.148286199366885</v>
       </c>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr"/>
@@ -64835,7 +64839,7 @@
         <v>233</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.0639326509939145</v>
+        <v>0.0639326509274414</v>
       </c>
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr"/>
@@ -65048,7 +65052,7 @@
         <v>221</v>
       </c>
       <c r="Q125" t="n">
-        <v>0.0731246733588764</v>
+        <v>0.0731246732899037</v>
       </c>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr"/>
@@ -65190,7 +65194,7 @@
         <v>263</v>
       </c>
       <c r="Q127" t="n">
-        <v>0.023549418090304</v>
+        <v>0.0235494180638203</v>
       </c>
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr"/>
@@ -65328,7 +65332,7 @@
         <v>186</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.1004758865645845</v>
+        <v>0.1004758864729852</v>
       </c>
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr"/>
@@ -65399,7 +65403,7 @@
         <v>180</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.1057158327925083</v>
+        <v>0.1057158324343914</v>
       </c>
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr"/>
@@ -65813,7 +65817,7 @@
         <v>209</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.0780979712771229</v>
+        <v>0.0780979713100205</v>
       </c>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr"/>
@@ -65884,7 +65888,7 @@
         <v>130</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.1749532200661109</v>
+        <v>0.1749532196644946</v>
       </c>
       <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr"/>
@@ -65951,7 +65955,7 @@
         <v>161</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.1375844245017798</v>
+        <v>0.1375844243827706</v>
       </c>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
@@ -66093,7 +66097,7 @@
         <v>226</v>
       </c>
       <c r="Q140" t="n">
-        <v>0.06790158709530091</v>
+        <v>0.0679015868006366</v>
       </c>
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr"/>
@@ -66164,7 +66168,7 @@
         <v>32</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.5627712299973278</v>
+        <v>0.5627712315558411</v>
       </c>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr"/>
@@ -66235,7 +66239,7 @@
         <v>44</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.4592891442365296</v>
+        <v>0.4592891445559759</v>
       </c>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr"/>
@@ -66306,7 +66310,7 @@
         <v>19</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.8210638736723673</v>
+        <v>0.8210638608013721</v>
       </c>
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr"/>
@@ -66377,7 +66381,7 @@
         <v>65</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.3330792580261453</v>
+        <v>0.3330792601913626</v>
       </c>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr"/>
@@ -66448,7 +66452,7 @@
         <v>37</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.4975762147374358</v>
+        <v>0.4975762132884682</v>
       </c>
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr"/>
@@ -66661,7 +66665,7 @@
         <v>84</v>
       </c>
       <c r="Q148" t="n">
-        <v>0.2815577213305332</v>
+        <v>0.2815577188726843</v>
       </c>
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr"/>
@@ -66732,7 +66736,7 @@
         <v>2</v>
       </c>
       <c r="Q149" t="n">
-        <v>1.919242557603348</v>
+        <v>1.919242556165218</v>
       </c>
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr"/>
@@ -66803,7 +66807,7 @@
         <v>1</v>
       </c>
       <c r="Q150" t="n">
-        <v>2.556123444338013</v>
+        <v>2.556123390077762</v>
       </c>
       <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr"/>
@@ -66870,7 +66874,7 @@
         <v>284</v>
       </c>
       <c r="Q151" t="n">
-        <v>0.0044335539387392</v>
+        <v>0.0044335539091265</v>
       </c>
       <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr"/>
@@ -66941,7 +66945,7 @@
         <v>10</v>
       </c>
       <c r="Q152" t="n">
-        <v>1.140998066750707</v>
+        <v>1.140998074803683</v>
       </c>
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr"/>
@@ -67012,7 +67016,7 @@
         <v>140</v>
       </c>
       <c r="Q153" t="n">
-        <v>0.1582518596799811</v>
+        <v>0.1582518595607535</v>
       </c>
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr"/>
@@ -67083,7 +67087,7 @@
         <v>3</v>
       </c>
       <c r="Q154" t="n">
-        <v>1.880651429423544</v>
+        <v>1.880651420627575</v>
       </c>
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr"/>
@@ -67154,7 +67158,7 @@
         <v>7</v>
       </c>
       <c r="Q155" t="n">
-        <v>1.469741870674143</v>
+        <v>1.469741850150696</v>
       </c>
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr"/>
@@ -67225,7 +67229,7 @@
         <v>8</v>
       </c>
       <c r="Q156" t="n">
-        <v>1.377636632610227</v>
+        <v>1.377636642232281</v>
       </c>
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr"/>
@@ -67296,7 +67300,7 @@
         <v>43</v>
       </c>
       <c r="Q157" t="n">
-        <v>0.4599585349714158</v>
+        <v>0.4599585288063763</v>
       </c>
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr"/>
@@ -67367,7 +67371,7 @@
         <v>9</v>
       </c>
       <c r="Q158" t="n">
-        <v>1.282669810425036</v>
+        <v>1.282669819237425</v>
       </c>
       <c r="R158" t="inlineStr">
         <is>
@@ -67442,7 +67446,7 @@
         <v>31</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.5710199182198941</v>
+        <v>0.5710199165154209</v>
       </c>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr"/>
@@ -67584,7 +67588,7 @@
         <v>28</v>
       </c>
       <c r="Q161" t="n">
-        <v>0.5921875177350278</v>
+        <v>0.5921875166908641</v>
       </c>
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr"/>
@@ -67655,7 +67659,7 @@
         <v>85</v>
       </c>
       <c r="Q162" t="n">
-        <v>0.2792724224492394</v>
+        <v>0.2792724228798964</v>
       </c>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr"/>
@@ -67726,7 +67730,7 @@
         <v>217</v>
       </c>
       <c r="Q163" t="n">
-        <v>0.0749492543789326</v>
+        <v>0.07494925401815331</v>
       </c>
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr"/>
@@ -67797,7 +67801,7 @@
         <v>12</v>
       </c>
       <c r="Q164" t="n">
-        <v>1.037891299550928</v>
+        <v>1.037891307294819</v>
       </c>
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr"/>
@@ -67868,7 +67872,7 @@
         <v>105</v>
       </c>
       <c r="Q165" t="n">
-        <v>0.2242611004723249</v>
+        <v>0.2242611020736249</v>
       </c>
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr"/>
@@ -67939,7 +67943,7 @@
         <v>20</v>
       </c>
       <c r="Q166" t="n">
-        <v>0.8126522627706078</v>
+        <v>0.8126522636883518</v>
       </c>
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr"/>
@@ -68010,7 +68014,7 @@
         <v>5</v>
       </c>
       <c r="Q167" t="n">
-        <v>1.524198154939078</v>
+        <v>1.524198158396275</v>
       </c>
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr"/>
@@ -68081,7 +68085,7 @@
         <v>47</v>
       </c>
       <c r="Q168" t="n">
-        <v>0.4273225220088224</v>
+        <v>0.4273225139056333</v>
       </c>
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr"/>
@@ -68152,7 +68156,7 @@
         <v>18</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.8812499624319454</v>
+        <v>0.8812499668146205</v>
       </c>
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr"/>
@@ -68223,7 +68227,7 @@
         <v>101</v>
       </c>
       <c r="Q170" t="n">
-        <v>0.2374324536469604</v>
+        <v>0.237432454230313</v>
       </c>
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr"/>
@@ -68294,7 +68298,7 @@
         <v>29</v>
       </c>
       <c r="Q171" t="n">
-        <v>0.5898551505653457</v>
+        <v>0.5898551502158805</v>
       </c>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr"/>
@@ -68365,7 +68369,7 @@
         <v>23</v>
       </c>
       <c r="Q172" t="n">
-        <v>0.6292713720177435</v>
+        <v>0.6292713719927117</v>
       </c>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr"/>
@@ -68436,7 +68440,7 @@
         <v>16</v>
       </c>
       <c r="Q173" t="n">
-        <v>0.8998323860578156</v>
+        <v>0.8998323900340969</v>
       </c>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr"/>
@@ -68507,7 +68511,7 @@
         <v>270</v>
       </c>
       <c r="Q174" t="n">
-        <v>0.0181465185156274</v>
+        <v>0.0181465184721985</v>
       </c>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr"/>
@@ -68578,7 +68582,7 @@
         <v>58</v>
       </c>
       <c r="Q175" t="n">
-        <v>0.3640186819625223</v>
+        <v>0.3640186838368973</v>
       </c>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr"/>
@@ -68649,7 +68653,7 @@
         <v>4</v>
       </c>
       <c r="Q176" t="n">
-        <v>1.777152360622422</v>
+        <v>1.777152407205172</v>
       </c>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr"/>
@@ -68720,7 +68724,7 @@
         <v>196</v>
       </c>
       <c r="Q177" t="n">
-        <v>0.08693091625279541</v>
+        <v>0.0869309193810036</v>
       </c>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr"/>
@@ -68787,7 +68791,7 @@
         <v>237</v>
       </c>
       <c r="Q178" t="n">
-        <v>0.0587628451378995</v>
+        <v>0.0587628452777346</v>
       </c>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr"/>
@@ -68858,7 +68862,7 @@
         <v>6</v>
       </c>
       <c r="Q179" t="n">
-        <v>1.501786877571854</v>
+        <v>1.501786849408398</v>
       </c>
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr"/>
@@ -68929,7 +68933,7 @@
         <v>52</v>
       </c>
       <c r="Q180" t="n">
-        <v>0.3962956317693583</v>
+        <v>0.3962956299745762</v>
       </c>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr"/>
@@ -69000,7 +69004,7 @@
         <v>36</v>
       </c>
       <c r="Q181" t="n">
-        <v>0.5076178727371301</v>
+        <v>0.5076178725980323</v>
       </c>
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr"/>
@@ -69071,7 +69075,7 @@
         <v>15</v>
       </c>
       <c r="Q182" t="n">
-        <v>0.9400679736331172</v>
+        <v>0.9400679612213904</v>
       </c>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr"/>
@@ -69209,7 +69213,7 @@
         <v>92</v>
       </c>
       <c r="Q184" t="n">
-        <v>0.2534444326551532</v>
+        <v>0.2534444336344664</v>
       </c>
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr"/>
@@ -69280,7 +69284,7 @@
         <v>42</v>
       </c>
       <c r="Q185" t="n">
-        <v>0.4743037729558964</v>
+        <v>0.4743037741500181</v>
       </c>
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr"/>
@@ -69489,7 +69493,7 @@
         <v>170</v>
       </c>
       <c r="Q188" t="n">
-        <v>0.1236486645090851</v>
+        <v>0.1236486643123691</v>
       </c>
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr"/>
@@ -69560,7 +69564,7 @@
         <v>122</v>
       </c>
       <c r="Q189" t="n">
-        <v>0.1866076008168487</v>
+        <v>0.1866076006743147</v>
       </c>
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr"/>
@@ -69702,7 +69706,7 @@
         <v>35</v>
       </c>
       <c r="Q191" t="n">
-        <v>0.5095875103746218</v>
+        <v>0.5095875148260584</v>
       </c>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
@@ -69844,7 +69848,7 @@
         <v>38</v>
       </c>
       <c r="Q193" t="n">
-        <v>0.497183176708147</v>
+        <v>0.4971831752197933</v>
       </c>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
@@ -69915,7 +69919,7 @@
         <v>262</v>
       </c>
       <c r="Q194" t="n">
-        <v>0.023949491158786</v>
+        <v>0.0239494911621264</v>
       </c>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
@@ -69986,7 +69990,7 @@
         <v>24</v>
       </c>
       <c r="Q195" t="n">
-        <v>0.6202993920433461</v>
+        <v>0.6202993909659184</v>
       </c>
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
@@ -70053,7 +70057,7 @@
         <v>205</v>
       </c>
       <c r="Q196" t="n">
-        <v>0.0818326987394478</v>
+        <v>0.0818326989764467</v>
       </c>
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr"/>
@@ -70195,7 +70199,7 @@
         <v>201</v>
       </c>
       <c r="Q198" t="n">
-        <v>0.0831454502779352</v>
+        <v>0.08314545096709861</v>
       </c>
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr"/>
@@ -70337,7 +70341,7 @@
         <v>40</v>
       </c>
       <c r="Q200" t="n">
-        <v>0.4839315754905064</v>
+        <v>0.4839315726841934</v>
       </c>
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
@@ -70408,7 +70412,7 @@
         <v>75</v>
       </c>
       <c r="Q201" t="n">
-        <v>0.2968206886197658</v>
+        <v>0.2968206885285421</v>
       </c>
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr"/>
@@ -70479,7 +70483,7 @@
         <v>77</v>
       </c>
       <c r="Q202" t="n">
-        <v>0.2958408817856502</v>
+        <v>0.2958408821914132</v>
       </c>
       <c r="R202" t="inlineStr"/>
       <c r="S202" t="inlineStr"/>
@@ -70550,7 +70554,7 @@
         <v>124</v>
       </c>
       <c r="Q203" t="n">
-        <v>0.1835649749010547</v>
+        <v>0.1835649748183185</v>
       </c>
       <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr"/>
@@ -70621,7 +70625,7 @@
         <v>188</v>
       </c>
       <c r="Q204" t="n">
-        <v>0.0977574325045181</v>
+        <v>0.097757432583382</v>
       </c>
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr"/>
@@ -70692,7 +70696,7 @@
         <v>72</v>
       </c>
       <c r="Q205" t="n">
-        <v>0.3017849286286974</v>
+        <v>0.3017849286565414</v>
       </c>
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr"/>
@@ -70763,7 +70767,7 @@
         <v>250</v>
       </c>
       <c r="Q206" t="n">
-        <v>0.0386996163281201</v>
+        <v>0.0386996169052657</v>
       </c>
       <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr"/>
@@ -70834,7 +70838,7 @@
         <v>280</v>
       </c>
       <c r="Q207" t="n">
-        <v>0.007856258761746599</v>
+        <v>0.0078562587612958</v>
       </c>
       <c r="R207" t="inlineStr"/>
       <c r="S207" t="inlineStr"/>
@@ -70905,7 +70909,7 @@
         <v>148</v>
       </c>
       <c r="Q208" t="n">
-        <v>0.1472292646650196</v>
+        <v>0.1472292669602828</v>
       </c>
       <c r="R208" t="inlineStr"/>
       <c r="S208" t="inlineStr"/>
@@ -70976,7 +70980,7 @@
         <v>126</v>
       </c>
       <c r="Q209" t="n">
-        <v>0.1831328395882209</v>
+        <v>0.1831328398845251</v>
       </c>
       <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr"/>
@@ -71047,7 +71051,7 @@
         <v>56</v>
       </c>
       <c r="Q210" t="n">
-        <v>0.3776954780160078</v>
+        <v>0.3776954779694583</v>
       </c>
       <c r="R210" t="inlineStr"/>
       <c r="S210" t="inlineStr"/>
@@ -71118,7 +71122,7 @@
         <v>142</v>
       </c>
       <c r="Q211" t="n">
-        <v>0.1570022741214908</v>
+        <v>0.1570022767967323</v>
       </c>
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr"/>
@@ -71260,7 +71264,7 @@
         <v>178</v>
       </c>
       <c r="Q213" t="n">
-        <v>0.1072195888303848</v>
+        <v>0.10721958774575</v>
       </c>
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr"/>
@@ -71331,7 +71335,7 @@
         <v>187</v>
       </c>
       <c r="Q214" t="n">
-        <v>0.0977994512645663</v>
+        <v>0.09779945062755969</v>
       </c>
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr"/>
@@ -71402,7 +71406,7 @@
         <v>116</v>
       </c>
       <c r="Q215" t="n">
-        <v>0.1931409358142398</v>
+        <v>0.1931409352115853</v>
       </c>
       <c r="R215" t="inlineStr"/>
       <c r="S215" t="inlineStr"/>
@@ -71548,7 +71552,7 @@
         <v>158</v>
       </c>
       <c r="Q217" t="n">
-        <v>0.138531363066001</v>
+        <v>0.1385313621226884</v>
       </c>
       <c r="R217" t="inlineStr"/>
       <c r="S217" t="inlineStr"/>
@@ -71690,7 +71694,7 @@
         <v>128</v>
       </c>
       <c r="Q219" t="n">
-        <v>0.1780255812380377</v>
+        <v>0.1780255811948261</v>
       </c>
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="inlineStr"/>
@@ -71757,7 +71761,7 @@
         <v>204</v>
       </c>
       <c r="Q220" t="n">
-        <v>0.0819291753926127</v>
+        <v>0.0819291751936594</v>
       </c>
       <c r="R220" t="inlineStr"/>
       <c r="S220" t="inlineStr"/>
@@ -71828,7 +71832,7 @@
         <v>282</v>
       </c>
       <c r="Q221" t="n">
-        <v>0.005548671419522</v>
+        <v>0.005548671434974</v>
       </c>
       <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr">
@@ -71899,7 +71903,7 @@
         <v>261</v>
       </c>
       <c r="Q222" t="n">
-        <v>0.026261927858936</v>
+        <v>0.0262619278602622</v>
       </c>
       <c r="R222" t="inlineStr"/>
       <c r="S222" t="inlineStr"/>
@@ -71970,7 +71974,7 @@
         <v>212</v>
       </c>
       <c r="Q223" t="n">
-        <v>0.0765677345914455</v>
+        <v>0.07656773429698729</v>
       </c>
       <c r="R223" t="inlineStr"/>
       <c r="S223" t="inlineStr"/>
@@ -72041,7 +72045,7 @@
         <v>67</v>
       </c>
       <c r="Q224" t="n">
-        <v>0.3230714467000144</v>
+        <v>0.3230714465913506</v>
       </c>
       <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr"/>
@@ -72112,7 +72116,7 @@
         <v>207</v>
       </c>
       <c r="Q225" t="n">
-        <v>0.0806726922545806</v>
+        <v>0.0806726918591051</v>
       </c>
       <c r="R225" t="inlineStr"/>
       <c r="S225" t="inlineStr"/>
@@ -72179,7 +72183,7 @@
         <v>121</v>
       </c>
       <c r="Q226" t="n">
-        <v>0.1873620199587518</v>
+        <v>0.1873620216892207</v>
       </c>
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr"/>
@@ -72250,7 +72254,7 @@
         <v>153</v>
       </c>
       <c r="Q227" t="n">
-        <v>0.1405164974587151</v>
+        <v>0.1405164927444923</v>
       </c>
       <c r="R227" t="inlineStr"/>
       <c r="S227" t="inlineStr"/>
@@ -72317,7 +72321,7 @@
         <v>97</v>
       </c>
       <c r="Q228" t="n">
-        <v>0.2458953673680066</v>
+        <v>0.2458953680628207</v>
       </c>
       <c r="R228" t="inlineStr"/>
       <c r="S228" t="inlineStr"/>
@@ -72388,7 +72392,7 @@
         <v>115</v>
       </c>
       <c r="Q229" t="n">
-        <v>0.1943648349511314</v>
+        <v>0.1943648353858606</v>
       </c>
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr"/>
@@ -72455,7 +72459,7 @@
         <v>62</v>
       </c>
       <c r="Q230" t="n">
-        <v>0.3476449030692279</v>
+        <v>0.3476449004457927</v>
       </c>
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr"/>
@@ -72593,7 +72597,7 @@
         <v>265</v>
       </c>
       <c r="Q232" t="n">
-        <v>0.0235318979273615</v>
+        <v>0.0235318979169753</v>
       </c>
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr"/>
@@ -72660,7 +72664,7 @@
         <v>232</v>
       </c>
       <c r="Q233" t="n">
-        <v>0.0652451465167162</v>
+        <v>0.0652451464467689</v>
       </c>
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr"/>
@@ -72731,7 +72735,7 @@
         <v>94</v>
       </c>
       <c r="Q234" t="n">
-        <v>0.2492573479165344</v>
+        <v>0.249257348266055</v>
       </c>
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr">
@@ -72944,7 +72948,7 @@
         <v>86</v>
       </c>
       <c r="Q237" t="n">
-        <v>0.2768393957228619</v>
+        <v>0.2768393968303386</v>
       </c>
       <c r="R237" t="inlineStr"/>
       <c r="S237" t="inlineStr"/>
@@ -73015,7 +73019,7 @@
         <v>99</v>
       </c>
       <c r="Q238" t="n">
-        <v>0.2449744204181269</v>
+        <v>0.244974419175426</v>
       </c>
       <c r="R238" t="inlineStr"/>
       <c r="S238" t="inlineStr"/>
@@ -73082,7 +73086,7 @@
         <v>136</v>
       </c>
       <c r="Q239" t="n">
-        <v>0.1627014038311406</v>
+        <v>0.1627014040699679</v>
       </c>
       <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr"/>
@@ -73153,7 +73157,7 @@
         <v>181</v>
       </c>
       <c r="Q240" t="n">
-        <v>0.1053753330613459</v>
+        <v>0.1053753327648039</v>
       </c>
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr"/>
@@ -73224,7 +73228,7 @@
         <v>76</v>
       </c>
       <c r="Q241" t="n">
-        <v>0.296085873792237</v>
+        <v>0.2960858717362686</v>
       </c>
       <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr"/>
@@ -73295,7 +73299,7 @@
         <v>132</v>
       </c>
       <c r="Q242" t="n">
-        <v>0.1694634482227854</v>
+        <v>0.1694634484563496</v>
       </c>
       <c r="R242" t="inlineStr"/>
       <c r="S242" t="inlineStr"/>
@@ -73366,7 +73370,7 @@
         <v>73</v>
       </c>
       <c r="Q243" t="n">
-        <v>0.3015858678524386</v>
+        <v>0.301585866946738</v>
       </c>
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr"/>
@@ -73437,7 +73441,7 @@
         <v>225</v>
       </c>
       <c r="Q244" t="n">
-        <v>0.0679641603803862</v>
+        <v>0.0679641603360446</v>
       </c>
       <c r="R244" t="inlineStr"/>
       <c r="S244" t="inlineStr"/>
@@ -73508,7 +73512,7 @@
         <v>159</v>
       </c>
       <c r="Q245" t="n">
-        <v>0.1385279927987609</v>
+        <v>0.1385279921868029</v>
       </c>
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr"/>
@@ -73579,7 +73583,7 @@
         <v>194</v>
       </c>
       <c r="Q246" t="n">
-        <v>0.0913271090438386</v>
+        <v>0.0913271083009398</v>
       </c>
       <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr"/>
@@ -73650,7 +73654,7 @@
         <v>149</v>
       </c>
       <c r="Q247" t="n">
-        <v>0.1465923640550767</v>
+        <v>0.1465923643965474</v>
       </c>
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr"/>
@@ -73721,7 +73725,7 @@
         <v>210</v>
       </c>
       <c r="Q248" t="n">
-        <v>0.077982623910039</v>
+        <v>0.0779826234157341</v>
       </c>
       <c r="R248" t="inlineStr"/>
       <c r="S248" t="inlineStr"/>
@@ -73792,7 +73796,7 @@
         <v>219</v>
       </c>
       <c r="Q249" t="n">
-        <v>0.0743105475993306</v>
+        <v>0.0743105475789269</v>
       </c>
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr"/>
@@ -73859,7 +73863,7 @@
         <v>114</v>
       </c>
       <c r="Q250" t="n">
-        <v>0.201061686448289</v>
+        <v>0.2010616854512954</v>
       </c>
       <c r="R250" t="inlineStr"/>
       <c r="S250" t="inlineStr"/>
@@ -73930,7 +73934,7 @@
         <v>157</v>
       </c>
       <c r="Q251" t="n">
-        <v>0.138630653955267</v>
+        <v>0.1386306574789947</v>
       </c>
       <c r="R251" t="inlineStr"/>
       <c r="S251" t="inlineStr"/>
@@ -74001,7 +74005,7 @@
         <v>64</v>
       </c>
       <c r="Q252" t="n">
-        <v>0.337075514072383</v>
+        <v>0.3370755130947255</v>
       </c>
       <c r="R252" t="inlineStr"/>
       <c r="S252" t="inlineStr"/>
@@ -74139,7 +74143,7 @@
         <v>271</v>
       </c>
       <c r="Q254" t="n">
-        <v>0.0175506450188389</v>
+        <v>0.0175506450188945</v>
       </c>
       <c r="R254" t="inlineStr"/>
       <c r="S254" t="inlineStr"/>
@@ -74281,7 +74285,7 @@
         <v>192</v>
       </c>
       <c r="Q256" t="n">
-        <v>0.09367680552210191</v>
+        <v>0.0936768053990623</v>
       </c>
       <c r="R256" t="inlineStr"/>
       <c r="S256" t="inlineStr"/>
@@ -74352,7 +74356,7 @@
         <v>129</v>
       </c>
       <c r="Q257" t="n">
-        <v>0.1757094803532384</v>
+        <v>0.1757094787449906</v>
       </c>
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr"/>
@@ -74423,7 +74427,7 @@
         <v>249</v>
       </c>
       <c r="Q258" t="n">
-        <v>0.0411389828607956</v>
+        <v>0.0411389826162849</v>
       </c>
       <c r="R258" t="inlineStr"/>
       <c r="S258" t="inlineStr"/>
@@ -74494,7 +74498,7 @@
         <v>87</v>
       </c>
       <c r="Q259" t="n">
-        <v>0.2697209009080312</v>
+        <v>0.2697209008190425</v>
       </c>
       <c r="R259" t="inlineStr"/>
       <c r="S259" t="inlineStr"/>
@@ -74565,7 +74569,7 @@
         <v>173</v>
       </c>
       <c r="Q260" t="n">
-        <v>0.1173256677180294</v>
+        <v>0.1173256670119973</v>
       </c>
       <c r="R260" t="inlineStr"/>
       <c r="S260" t="inlineStr"/>
@@ -74636,7 +74640,7 @@
         <v>215</v>
       </c>
       <c r="Q261" t="n">
-        <v>0.0753540098620796</v>
+        <v>0.0753540092661287</v>
       </c>
       <c r="R261" t="inlineStr"/>
       <c r="S261" t="inlineStr"/>
@@ -74707,7 +74711,7 @@
         <v>182</v>
       </c>
       <c r="Q262" t="n">
-        <v>0.1030287581695301</v>
+        <v>0.1030287559047355</v>
       </c>
       <c r="R262" t="inlineStr"/>
       <c r="S262" t="inlineStr"/>
@@ -74778,7 +74782,7 @@
         <v>96</v>
       </c>
       <c r="Q263" t="n">
-        <v>0.2473384922348745</v>
+        <v>0.2473384921530617</v>
       </c>
       <c r="R263" t="inlineStr"/>
       <c r="S263" t="inlineStr"/>
@@ -74849,7 +74853,7 @@
         <v>193</v>
       </c>
       <c r="Q264" t="n">
-        <v>0.09208494369697789</v>
+        <v>0.0920849446228016</v>
       </c>
       <c r="R264" t="inlineStr"/>
       <c r="S264" t="inlineStr"/>
@@ -74920,7 +74924,7 @@
         <v>112</v>
       </c>
       <c r="Q265" t="n">
-        <v>0.2063119366826543</v>
+        <v>0.2063119394060513</v>
       </c>
       <c r="R265" t="inlineStr"/>
       <c r="S265" t="inlineStr"/>
@@ -75062,7 +75066,7 @@
         <v>240</v>
       </c>
       <c r="Q267" t="n">
-        <v>0.0566650216505879</v>
+        <v>0.0566650219443807</v>
       </c>
       <c r="R267" t="inlineStr"/>
       <c r="S267" t="inlineStr"/>
@@ -75133,7 +75137,7 @@
         <v>184</v>
       </c>
       <c r="Q268" t="n">
-        <v>0.1021459260291637</v>
+        <v>0.102145926029326</v>
       </c>
       <c r="R268" t="inlineStr"/>
       <c r="S268" t="inlineStr"/>
@@ -75204,7 +75208,7 @@
         <v>268</v>
       </c>
       <c r="Q269" t="n">
-        <v>0.0192505707720816</v>
+        <v>0.019250570681627</v>
       </c>
       <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr"/>
@@ -75275,7 +75279,7 @@
         <v>71</v>
       </c>
       <c r="Q270" t="n">
-        <v>0.3127512332561439</v>
+        <v>0.3127512329397147</v>
       </c>
       <c r="R270" t="inlineStr"/>
       <c r="S270" t="inlineStr"/>
@@ -75342,7 +75346,7 @@
         <v>123</v>
       </c>
       <c r="Q271" t="n">
-        <v>0.1862284116855768</v>
+        <v>0.1862284136412526</v>
       </c>
       <c r="R271" t="inlineStr"/>
       <c r="S271" t="inlineStr"/>
@@ -75413,7 +75417,7 @@
         <v>102</v>
       </c>
       <c r="Q272" t="n">
-        <v>0.2372985461520635</v>
+        <v>0.237298538023274</v>
       </c>
       <c r="R272" t="inlineStr"/>
       <c r="S272" t="inlineStr"/>
@@ -75555,7 +75559,7 @@
         <v>89</v>
       </c>
       <c r="Q274" t="n">
-        <v>0.2662596818352701</v>
+        <v>0.2662596864344671</v>
       </c>
       <c r="R274" t="inlineStr">
         <is>
@@ -75634,7 +75638,7 @@
         <v>131</v>
       </c>
       <c r="Q275" t="n">
-        <v>0.1731717319971636</v>
+        <v>0.173171732063121</v>
       </c>
       <c r="R275" t="inlineStr"/>
       <c r="S275" t="inlineStr"/>
@@ -75705,7 +75709,7 @@
         <v>63</v>
       </c>
       <c r="Q276" t="n">
-        <v>0.3453992968560903</v>
+        <v>0.345399298867179</v>
       </c>
       <c r="R276" t="inlineStr"/>
       <c r="S276" t="inlineStr"/>
@@ -75776,7 +75780,7 @@
         <v>145</v>
       </c>
       <c r="Q277" t="n">
-        <v>0.1518432337423133</v>
+        <v>0.151843234871835</v>
       </c>
       <c r="R277" t="inlineStr"/>
       <c r="S277" t="inlineStr"/>
@@ -75847,7 +75851,7 @@
         <v>206</v>
       </c>
       <c r="Q278" t="n">
-        <v>0.0806990752111956</v>
+        <v>0.0806990758127737</v>
       </c>
       <c r="R278" t="inlineStr"/>
       <c r="S278" t="inlineStr"/>
@@ -75918,7 +75922,7 @@
         <v>118</v>
       </c>
       <c r="Q279" t="n">
-        <v>0.1907238515976559</v>
+        <v>0.1907238530404656</v>
       </c>
       <c r="R279" t="inlineStr"/>
       <c r="S279" t="inlineStr"/>
@@ -75989,7 +75993,7 @@
         <v>254</v>
       </c>
       <c r="Q280" t="n">
-        <v>0.0347291478441294</v>
+        <v>0.034729147869885</v>
       </c>
       <c r="R280" t="inlineStr"/>
       <c r="S280" t="inlineStr"/>
@@ -76131,7 +76135,7 @@
         <v>239</v>
       </c>
       <c r="Q282" t="n">
-        <v>0.0576338045515062</v>
+        <v>0.0576338050170916</v>
       </c>
       <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr"/>
@@ -76202,7 +76206,7 @@
         <v>218</v>
       </c>
       <c r="Q283" t="n">
-        <v>0.0747194172238712</v>
+        <v>0.0747194172284599</v>
       </c>
       <c r="R283" t="inlineStr"/>
       <c r="S283" t="inlineStr"/>
@@ -76344,7 +76348,7 @@
         <v>198</v>
       </c>
       <c r="Q285" t="n">
-        <v>0.0856255835115789</v>
+        <v>0.08562558450385881</v>
       </c>
       <c r="R285" t="inlineStr"/>
       <c r="S285" t="inlineStr"/>
@@ -76415,7 +76419,7 @@
         <v>185</v>
       </c>
       <c r="Q286" t="n">
-        <v>0.101334922074056</v>
+        <v>0.1013349225335817</v>
       </c>
       <c r="R286" t="inlineStr"/>
       <c r="S286" t="inlineStr"/>
@@ -76557,7 +76561,7 @@
         <v>245</v>
       </c>
       <c r="Q288" t="n">
-        <v>0.0463521265005554</v>
+        <v>0.0463521270619127</v>
       </c>
       <c r="R288" t="inlineStr"/>
       <c r="S288" t="inlineStr"/>
@@ -76628,7 +76632,7 @@
         <v>259</v>
       </c>
       <c r="Q289" t="n">
-        <v>0.0288976473724475</v>
+        <v>0.0288976474139661</v>
       </c>
       <c r="R289" t="inlineStr"/>
       <c r="S289" t="inlineStr"/>
@@ -76699,7 +76703,7 @@
         <v>168</v>
       </c>
       <c r="Q290" t="n">
-        <v>0.1256378592876022</v>
+        <v>0.1256378601484289</v>
       </c>
       <c r="R290" t="inlineStr"/>
       <c r="S290" t="inlineStr"/>
@@ -77188,7 +77192,7 @@
         <v>163</v>
       </c>
       <c r="Q297" t="n">
-        <v>0.1355131278345899</v>
+        <v>0.1355131279515838</v>
       </c>
       <c r="R297" t="inlineStr"/>
       <c r="S297" t="inlineStr"/>
@@ -77259,7 +77263,7 @@
         <v>247</v>
       </c>
       <c r="Q298" t="n">
-        <v>0.0451915622436144</v>
+        <v>0.0451915621107183</v>
       </c>
       <c r="R298" t="inlineStr"/>
       <c r="S298" t="inlineStr"/>
@@ -77330,7 +77334,7 @@
         <v>81</v>
       </c>
       <c r="Q299" t="n">
-        <v>0.2914386651374229</v>
+        <v>0.2914386650696634</v>
       </c>
       <c r="R299" t="inlineStr"/>
       <c r="S299" t="inlineStr"/>
@@ -77401,7 +77405,7 @@
         <v>139</v>
       </c>
       <c r="Q300" t="n">
-        <v>0.1596449439516595</v>
+        <v>0.1596449444341947</v>
       </c>
       <c r="R300" t="inlineStr"/>
       <c r="S300" t="inlineStr"/>
@@ -77539,7 +77543,7 @@
         <v>248</v>
       </c>
       <c r="Q302" t="n">
-        <v>0.0440145876976862</v>
+        <v>0.0440145874194997</v>
       </c>
       <c r="R302" t="inlineStr"/>
       <c r="S302" t="inlineStr"/>
@@ -77610,7 +77614,7 @@
         <v>273</v>
       </c>
       <c r="Q303" t="n">
-        <v>0.0151811850298901</v>
+        <v>0.0151811849810569</v>
       </c>
       <c r="R303" t="inlineStr"/>
       <c r="S303" t="inlineStr"/>
@@ -77752,7 +77756,7 @@
         <v>190</v>
       </c>
       <c r="Q305" t="n">
-        <v>0.096704997675365</v>
+        <v>0.0967049982362356</v>
       </c>
       <c r="R305" t="inlineStr"/>
       <c r="S305" t="inlineStr"/>
@@ -77823,7 +77827,7 @@
         <v>266</v>
       </c>
       <c r="Q306" t="n">
-        <v>0.02219788394318</v>
+        <v>0.0221978839975276</v>
       </c>
       <c r="R306" t="inlineStr"/>
       <c r="S306" t="inlineStr"/>
@@ -77894,7 +77898,7 @@
         <v>176</v>
       </c>
       <c r="Q307" t="n">
-        <v>0.113590097551741</v>
+        <v>0.1135900977478483</v>
       </c>
       <c r="R307" t="inlineStr"/>
       <c r="S307" t="inlineStr"/>
@@ -78036,7 +78040,7 @@
         <v>195</v>
       </c>
       <c r="Q309" t="n">
-        <v>0.0883472094946131</v>
+        <v>0.08834720974877849</v>
       </c>
       <c r="R309" t="inlineStr"/>
       <c r="S309" t="inlineStr"/>
@@ -78178,7 +78182,7 @@
         <v>155</v>
       </c>
       <c r="Q311" t="n">
-        <v>0.1396996326834606</v>
+        <v>0.1396996331391438</v>
       </c>
       <c r="R311" t="inlineStr"/>
       <c r="S311" t="inlineStr"/>
@@ -78249,7 +78253,7 @@
         <v>167</v>
       </c>
       <c r="Q312" t="n">
-        <v>0.1257618505741137</v>
+        <v>0.1257618508417461</v>
       </c>
       <c r="R312" t="inlineStr"/>
       <c r="S312" t="inlineStr"/>
@@ -78320,7 +78324,7 @@
         <v>251</v>
       </c>
       <c r="Q313" t="n">
-        <v>0.0376778506200125</v>
+        <v>0.0376778504670044</v>
       </c>
       <c r="R313" t="inlineStr"/>
       <c r="S313" t="inlineStr"/>
@@ -78391,7 +78395,7 @@
         <v>241</v>
       </c>
       <c r="Q314" t="n">
-        <v>0.0546734455919884</v>
+        <v>0.0546734459412497</v>
       </c>
       <c r="R314" t="inlineStr"/>
       <c r="S314" t="inlineStr"/>
@@ -78533,7 +78537,7 @@
         <v>260</v>
       </c>
       <c r="Q316" t="n">
-        <v>0.0287638861829401</v>
+        <v>0.0287638861947618</v>
       </c>
       <c r="R316" t="inlineStr"/>
       <c r="S316" t="inlineStr"/>
@@ -78746,7 +78750,7 @@
         <v>74</v>
       </c>
       <c r="Q319" t="n">
-        <v>0.3009598605665321</v>
+        <v>0.3009598608937349</v>
       </c>
       <c r="R319" t="inlineStr"/>
       <c r="S319" t="inlineStr"/>
@@ -78817,7 +78821,7 @@
         <v>214</v>
       </c>
       <c r="Q320" t="n">
-        <v>0.0755991041030822</v>
+        <v>0.0755991042067778</v>
       </c>
       <c r="R320" t="inlineStr"/>
       <c r="S320" t="inlineStr"/>
@@ -78884,7 +78888,7 @@
         <v>258</v>
       </c>
       <c r="Q321" t="n">
-        <v>0.0291250391668336</v>
+        <v>0.0291250390900226</v>
       </c>
       <c r="R321" t="inlineStr"/>
       <c r="S321" t="inlineStr"/>
@@ -78955,7 +78959,7 @@
         <v>133</v>
       </c>
       <c r="Q322" t="n">
-        <v>0.1693370981143288</v>
+        <v>0.1693370974912838</v>
       </c>
       <c r="R322" t="inlineStr"/>
       <c r="S322" t="inlineStr"/>
@@ -79026,7 +79030,7 @@
         <v>51</v>
       </c>
       <c r="Q323" t="n">
-        <v>0.403069786815397</v>
+        <v>0.4030697872878174</v>
       </c>
       <c r="R323" t="inlineStr"/>
       <c r="S323" t="inlineStr"/>
@@ -79097,7 +79101,7 @@
         <v>165</v>
       </c>
       <c r="Q324" t="n">
-        <v>0.1291983064427726</v>
+        <v>0.1291983064522342</v>
       </c>
       <c r="R324" t="inlineStr"/>
       <c r="S324" t="inlineStr"/>
@@ -79168,7 +79172,7 @@
         <v>171</v>
       </c>
       <c r="Q325" t="n">
-        <v>0.1181148920953586</v>
+        <v>0.1181148923334288</v>
       </c>
       <c r="R325" t="inlineStr"/>
       <c r="S325" t="inlineStr"/>
@@ -79239,7 +79243,7 @@
         <v>216</v>
       </c>
       <c r="Q326" t="n">
-        <v>0.0752790370236734</v>
+        <v>0.0752790370814214</v>
       </c>
       <c r="R326" t="inlineStr"/>
       <c r="S326" t="inlineStr"/>
@@ -79310,7 +79314,7 @@
         <v>231</v>
       </c>
       <c r="Q327" t="n">
-        <v>0.0658087163960762</v>
+        <v>0.06580871670546611</v>
       </c>
       <c r="R327" t="inlineStr"/>
       <c r="S327" t="inlineStr"/>
@@ -79381,7 +79385,7 @@
         <v>238</v>
       </c>
       <c r="Q328" t="n">
-        <v>0.0583611294448093</v>
+        <v>0.0583611289704404</v>
       </c>
       <c r="R328" t="inlineStr"/>
       <c r="S328" t="inlineStr"/>
@@ -79452,7 +79456,7 @@
         <v>200</v>
       </c>
       <c r="Q329" t="n">
-        <v>0.0842335701936059</v>
+        <v>0.08423356914425879</v>
       </c>
       <c r="R329" t="inlineStr"/>
       <c r="S329" t="inlineStr"/>
@@ -79523,7 +79527,7 @@
         <v>11</v>
       </c>
       <c r="Q330" t="n">
-        <v>1.128056554324097</v>
+        <v>1.128056553111823</v>
       </c>
       <c r="R330" t="inlineStr"/>
       <c r="S330" t="inlineStr"/>
@@ -79594,7 +79598,7 @@
         <v>269</v>
       </c>
       <c r="Q331" t="n">
-        <v>0.0181864593511464</v>
+        <v>0.0181864595055796</v>
       </c>
       <c r="R331" t="inlineStr"/>
       <c r="S331" t="inlineStr"/>
@@ -79665,7 +79669,7 @@
         <v>110</v>
       </c>
       <c r="Q332" t="n">
-        <v>0.2179315828758856</v>
+        <v>0.2179315812532847</v>
       </c>
       <c r="R332" t="inlineStr"/>
       <c r="S332" t="inlineStr"/>
@@ -79736,7 +79740,7 @@
         <v>137</v>
       </c>
       <c r="Q333" t="n">
-        <v>0.1624315873032645</v>
+        <v>0.1624315874369763</v>
       </c>
       <c r="R333" t="inlineStr"/>
       <c r="S333" t="inlineStr"/>
@@ -79807,7 +79811,7 @@
         <v>91</v>
       </c>
       <c r="Q334" t="n">
-        <v>0.2612608738288006</v>
+        <v>0.2612608733556462</v>
       </c>
       <c r="R334" t="inlineStr"/>
       <c r="S334" t="inlineStr"/>
@@ -79878,7 +79882,7 @@
         <v>134</v>
       </c>
       <c r="Q335" t="n">
-        <v>0.1690928723903345</v>
+        <v>0.169092871564394</v>
       </c>
       <c r="R335" t="inlineStr"/>
       <c r="S335" t="inlineStr"/>
@@ -79949,7 +79953,7 @@
         <v>227</v>
       </c>
       <c r="Q336" t="n">
-        <v>0.0676257319009077</v>
+        <v>0.0676257322124774</v>
       </c>
       <c r="R336" t="inlineStr"/>
       <c r="S336" t="inlineStr"/>
@@ -80158,7 +80162,7 @@
         <v>41</v>
       </c>
       <c r="Q339" t="n">
-        <v>0.4819144059178167</v>
+        <v>0.481914403524861</v>
       </c>
       <c r="R339" t="inlineStr"/>
       <c r="S339" t="inlineStr"/>
@@ -80225,7 +80229,7 @@
         <v>93</v>
       </c>
       <c r="Q340" t="n">
-        <v>0.2500687755865019</v>
+        <v>0.2500687747465059</v>
       </c>
       <c r="R340" t="inlineStr"/>
       <c r="S340" t="inlineStr"/>
@@ -80367,7 +80371,7 @@
         <v>279</v>
       </c>
       <c r="Q342" t="n">
-        <v>0.0096271406732358</v>
+        <v>0.009627140665729001</v>
       </c>
       <c r="R342" t="inlineStr"/>
       <c r="S342" t="inlineStr"/>
@@ -80438,7 +80442,7 @@
         <v>257</v>
       </c>
       <c r="Q343" t="n">
-        <v>0.0300510154764377</v>
+        <v>0.0300510154492188</v>
       </c>
       <c r="R343" t="inlineStr"/>
       <c r="S343" t="inlineStr"/>
@@ -80509,7 +80513,7 @@
         <v>229</v>
       </c>
       <c r="Q344" t="n">
-        <v>0.0668342432701631</v>
+        <v>0.0668342434009984</v>
       </c>
       <c r="R344" t="inlineStr"/>
       <c r="S344" t="inlineStr"/>
@@ -80580,7 +80584,7 @@
         <v>281</v>
       </c>
       <c r="Q345" t="n">
-        <v>0.0078485637150721</v>
+        <v>0.007848563710024299</v>
       </c>
       <c r="R345" t="inlineStr"/>
       <c r="S345" t="inlineStr"/>
@@ -80651,7 +80655,7 @@
         <v>83</v>
       </c>
       <c r="Q346" t="n">
-        <v>0.2843659083005886</v>
+        <v>0.2843659090098198</v>
       </c>
       <c r="R346" t="inlineStr"/>
       <c r="S346" t="inlineStr"/>
@@ -80722,7 +80726,7 @@
         <v>108</v>
       </c>
       <c r="Q347" t="n">
-        <v>0.2224843674390065</v>
+        <v>0.2224843685152405</v>
       </c>
       <c r="R347" t="inlineStr"/>
       <c r="S347" t="inlineStr"/>
@@ -80793,7 +80797,7 @@
         <v>197</v>
       </c>
       <c r="Q348" t="n">
-        <v>0.08649926423334291</v>
+        <v>0.0864992646664024</v>
       </c>
       <c r="R348" t="inlineStr"/>
       <c r="S348" t="inlineStr"/>
@@ -80935,7 +80939,7 @@
         <v>111</v>
       </c>
       <c r="Q350" t="n">
-        <v>0.2068253690971373</v>
+        <v>0.2068253683462282</v>
       </c>
       <c r="R350" t="inlineStr"/>
       <c r="S350" t="inlineStr"/>
@@ -81006,7 +81010,7 @@
         <v>70</v>
       </c>
       <c r="Q351" t="n">
-        <v>0.3177488903595923</v>
+        <v>0.3177488903567858</v>
       </c>
       <c r="R351" t="inlineStr"/>
       <c r="S351" t="inlineStr"/>
@@ -81077,7 +81081,7 @@
         <v>213</v>
       </c>
       <c r="Q352" t="n">
-        <v>0.0758838494979911</v>
+        <v>0.0758838492508879</v>
       </c>
       <c r="R352" t="inlineStr"/>
       <c r="S352" t="inlineStr"/>
@@ -81148,7 +81152,7 @@
         <v>144</v>
       </c>
       <c r="Q353" t="n">
-        <v>0.1524631752926004</v>
+        <v>0.152463175327636</v>
       </c>
       <c r="R353" t="inlineStr"/>
       <c r="S353" t="inlineStr"/>
@@ -81219,7 +81223,7 @@
         <v>143</v>
       </c>
       <c r="Q354" t="n">
-        <v>0.1566409634091377</v>
+        <v>0.156640965106948</v>
       </c>
       <c r="R354" t="inlineStr"/>
       <c r="S354" t="inlineStr"/>
@@ -81290,7 +81294,7 @@
         <v>236</v>
       </c>
       <c r="Q355" t="n">
-        <v>0.0592101211106404</v>
+        <v>0.0592101205162679</v>
       </c>
       <c r="R355" t="inlineStr"/>
       <c r="S355" t="inlineStr"/>
@@ -81361,7 +81365,7 @@
         <v>275</v>
       </c>
       <c r="Q356" t="n">
-        <v>0.0117804912169294</v>
+        <v>0.0117804912145817</v>
       </c>
       <c r="R356" t="inlineStr"/>
       <c r="S356" t="inlineStr"/>
@@ -81570,7 +81574,7 @@
         <v>264</v>
       </c>
       <c r="Q359" t="n">
-        <v>0.0235473866188571</v>
+        <v>0.0235473866647673</v>
       </c>
       <c r="R359" t="inlineStr"/>
       <c r="S359" t="inlineStr">
@@ -81612,30 +81616,34 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
+          <t>(비활성화)</t>
+        </is>
+      </c>
+      <c r="J360" t="b">
+        <v>1</v>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>중복 통합(비활성화)</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>#853과 같은 의도(죽는 시점·방식) 중복</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>중복 통합(#853) · 신규 S013(Aron 36문항)과 주제 겹침</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
           <t>100살까지 사는 것과 건강하게 80살까지 사는 것 중 뭐가 더 나은가요?</t>
         </is>
       </c>
-      <c r="J360" t="b">
-        <v>1</v>
-      </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t>재작성</t>
-        </is>
-      </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t>#853과 같은 의도(죽는 시점·방식) 중복</t>
-        </is>
-      </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>중복 해소 → 다른 각도의 양자택일</t>
-        </is>
-      </c>
-      <c r="N360" t="inlineStr"/>
       <c r="O360" t="n">
-        <v>-5.704492715057147</v>
+        <v>0</v>
       </c>
       <c r="P360" t="n">
         <v>351</v>
@@ -81708,7 +81716,7 @@
         <v>242</v>
       </c>
       <c r="Q361" t="n">
-        <v>0.0526795752072951</v>
+        <v>0.0526795752080927</v>
       </c>
       <c r="R361" t="inlineStr"/>
       <c r="S361" t="inlineStr"/>
@@ -81779,7 +81787,7 @@
         <v>172</v>
       </c>
       <c r="Q362" t="n">
-        <v>0.1174078878647791</v>
+        <v>0.1174078878093762</v>
       </c>
       <c r="R362" t="inlineStr"/>
       <c r="S362" t="inlineStr"/>
@@ -81992,7 +82000,7 @@
         <v>235</v>
       </c>
       <c r="Q365" t="n">
-        <v>0.0614316358853387</v>
+        <v>0.061431635970571</v>
       </c>
       <c r="R365" t="inlineStr"/>
       <c r="S365" t="inlineStr"/>
@@ -82063,7 +82071,7 @@
         <v>255</v>
       </c>
       <c r="Q366" t="n">
-        <v>0.0343081282459821</v>
+        <v>0.034308128156838</v>
       </c>
       <c r="R366" t="inlineStr"/>
       <c r="S366" t="inlineStr"/>
@@ -82134,7 +82142,7 @@
         <v>246</v>
       </c>
       <c r="Q367" t="n">
-        <v>0.0456713533827165</v>
+        <v>0.0456713534194809</v>
       </c>
       <c r="R367" t="inlineStr"/>
       <c r="S367" t="inlineStr"/>
@@ -82205,7 +82213,7 @@
         <v>223</v>
       </c>
       <c r="Q368" t="n">
-        <v>0.0718934098385287</v>
+        <v>0.0718934099020183</v>
       </c>
       <c r="R368" t="inlineStr"/>
       <c r="S368" t="inlineStr"/>
@@ -82351,7 +82359,7 @@
         <v>191</v>
       </c>
       <c r="Q370" t="n">
-        <v>0.0937425578999284</v>
+        <v>0.093742557992453</v>
       </c>
       <c r="R370" t="inlineStr"/>
       <c r="S370" t="inlineStr"/>
@@ -82422,7 +82430,7 @@
         <v>151</v>
       </c>
       <c r="Q371" t="n">
-        <v>0.1410664284728315</v>
+        <v>0.1410664286786173</v>
       </c>
       <c r="R371" t="inlineStr"/>
       <c r="S371" t="inlineStr"/>
@@ -82493,7 +82501,7 @@
         <v>253</v>
       </c>
       <c r="Q372" t="n">
-        <v>0.0373003260338959</v>
+        <v>0.0373003260791848</v>
       </c>
       <c r="R372" t="inlineStr"/>
       <c r="S372" t="inlineStr"/>
@@ -82635,7 +82643,7 @@
         <v>135</v>
       </c>
       <c r="Q374" t="n">
-        <v>0.1632608861421532</v>
+        <v>0.1632608862248837</v>
       </c>
       <c r="R374" t="inlineStr"/>
       <c r="S374" t="inlineStr"/>
@@ -82706,7 +82714,7 @@
         <v>272</v>
       </c>
       <c r="Q375" t="n">
-        <v>0.0153991068616709</v>
+        <v>0.0153991068812722</v>
       </c>
       <c r="R375" t="inlineStr"/>
       <c r="S375" t="inlineStr"/>
@@ -82777,7 +82785,7 @@
         <v>278</v>
       </c>
       <c r="Q376" t="n">
-        <v>0.009663534114362</v>
+        <v>0.009663534128441899</v>
       </c>
       <c r="R376" t="inlineStr"/>
       <c r="S376" t="inlineStr"/>
